--- a/Contenidos_mas_disparados/output/contenidos_consultados_detalle_mayo_2026.xlsx
+++ b/Contenidos_mas_disparados/output/contenidos_consultados_detalle_mayo_2026.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E889"/>
+  <dimension ref="A1:E898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B1" s="2" t="n">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coyuntura Extensión Horaria Línea D [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>Efemérides y OB Temáticos</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -769,7 +769,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SUA01CUX04 Apertura - Auto mal estacionado</t>
+          <t>SUA01CUX04 Apertura - Auto mal estacionado (NUEVO)</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>15219</v>
+        <v>15216</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.006174011464456533</v>
+        <v>0.006172794430854236</v>
       </c>
     </row>
     <row r="31">
@@ -899,27 +899,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUACI Componentes Comunes</t>
+          <t>TUR01CUX01 Apertura - Turno Nuevo ejemplar DNI</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>13017</v>
+        <v>12714</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.005280708800369978</v>
+        <v>0.005157788406537905</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TUR01CUX01 Apertura - Turno Nuevo ejemplar DNI</t>
+          <t>SUACI Componentes Comunes</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>12714</v>
+        <v>12569</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.005157788406537905</v>
+        <v>0.00509896511576018</v>
       </c>
     </row>
     <row r="37">
@@ -1497,14 +1497,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IN01CUX01 Cómo pagar legajos - Infracciones, Derivación a agente de Infracciones</t>
+          <t>IN01CUX01 Cómo pagar legajos - Infracciones</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>0.001412164656532834</v>
+        <v>0.001412570334400266</v>
       </c>
     </row>
     <row r="82">
@@ -1653,7 +1653,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OB05CUX02 Apertura - Super Apertura Obras - DGROC</t>
+          <t>12. Entradas BA</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -1666,7 +1666,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12. Entradas BA</t>
+          <t>OB05CUX02 Apertura - Super Apertura Obras - DGROC</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>2520</v>
+        <v>2563</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>0.001022308225930118</v>
+        <v>0.001039752374229719</v>
       </c>
     </row>
     <row r="96">
@@ -1718,40 +1718,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TUR01CUX05 Validar datos - Turno para renovación de licencia de conducir</t>
+          <t>AG01CUX01 Patentes - AGIP</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>2442</v>
+        <v>2380</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>0.0009906653522703762</v>
+        <v>0.0009655133244895559</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AG01CUX01 Patentes - AGIP</t>
+          <t>EM02CUX01 Superapertura empleo - Búsqueda de trabajo en la Ciudad</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>2380</v>
+        <v>2274</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>0.0009655133244895559</v>
+        <v>0.0009225114705417016</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EM02CUX01 Superapertura empleo - Búsqueda de trabajo en la Ciudad</t>
+          <t>TUR01CUX05 Validar datos - Turno para renovación de licencia de conducir</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
-        <v>2274</v>
+        <v>2158</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>0.0009225114705417016</v>
+        <v>0.0008754528379195216</v>
       </c>
     </row>
     <row r="101">
@@ -1809,7 +1809,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SA01CUX06  Apertura - Vacunación COVID-19 ??</t>
+          <t>SA01CUX06  Apertura - Vacunación COVID-19 💉</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -1861,27 +1861,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TR04CUX23 Apertura - Boleta BUI</t>
+          <t>17. Turnos abiertos</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>0.0007273804163066275</v>
+        <v>0.0007314371949809534</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>17. Turnos abiertos</t>
+          <t>TR04CUX23 Apertura - Boleta BUI</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
-        <v>1786</v>
+        <v>1793</v>
       </c>
       <c r="C110" s="6" t="n">
-        <v>0.0007245406712345994</v>
+        <v>0.0007273804163066275</v>
       </c>
     </row>
     <row r="111">
@@ -1965,7 +1965,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DEC02CUX02 Apertura - Plan de Transformación del Microcentro ??</t>
+          <t>DEC02CUX02 Apertura - Plan de Transformación del Microcentro 🚀</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -2056,79 +2056,79 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>03. MO08CUX03 - AUSA - Sacar TelePASE</t>
+          <t>MO08CUX01 Pagar de otra forma - RUTRAMUR</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>0.0006133849355580707</v>
+        <v>0.0006113565462209079</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MO08CUX01 Pagar de otra forma - RUTRAMUR</t>
+          <t>05. MO05CUX05 LIC00CUX00 Renovación Licencia Experiencia Unificada</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>1507</v>
+        <v>1482</v>
       </c>
       <c r="C125" s="6" t="n">
-        <v>0.0006113565462209079</v>
+        <v>0.0006012145995350932</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>05. MO05CUX05 LIC00CUX00 Renovación Licencia Experiencia Unificada</t>
+          <t>TUR01CUX08 Sacar turno - Turno para pasaporte</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>1482</v>
+        <v>1467</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>0.0006012145995350932</v>
+        <v>0.0005951294315236044</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TUR01CUX08 Sacar turno - Turno para pasaporte</t>
+          <t>SE02CUX03 Estafas TelePASE - Estafas en Infracciones y VTV</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>1467</v>
+        <v>1449</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>0.0005951294315236044</v>
+        <v>0.0005878272299098178</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SE02CUX03 Estafas TelePASE - Estafas en Infracciones y VTV</t>
+          <t>03. AGC03CUX03 - Carnet Manipulador de Alimentos</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="C128" s="6" t="n">
-        <v>0.0005878272299098178</v>
+        <v>0.0005853931627052223</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>03. AGC03CUX03 - Carnet Manipulador de Alimentos</t>
+          <t>03. MO08CUX03 - AUSA - Sacar TelePASE</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>1443</v>
+        <v>1421</v>
       </c>
       <c r="C129" s="6" t="n">
-        <v>0.0005853931627052223</v>
+        <v>0.0005764682496217054</v>
       </c>
     </row>
     <row r="130">
@@ -2160,7 +2160,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CIU05CUX03 Retiro - Belgrano</t>
+          <t>CIU05CUX03 Retiro - Palermo</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
@@ -2316,7 +2316,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DEC02CUX01 Apertura - Distrito del Vino ??</t>
+          <t>DEC02CUX01 Apertura - Distrito del Vino 🍷</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
@@ -2394,7 +2394,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TR04CUX11 Apertura - Casamientos ??</t>
+          <t>TR04CUX11 Apertura - Casamientos 💍</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
@@ -2433,72 +2433,72 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01. DE03CUX1 Piletas de la ciudad</t>
+          <t>TR03CUX17 Permiso de carga excepcional (por viaje) - Desarrollo urbano y transporte - Transporte</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C153" s="6" t="n">
-        <v>0.0004093289682394798</v>
+        <v>0.0004097346461069124</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>07. MO04CUX07 - Permitido estacionar</t>
+          <t>01. DE03CUX1 Piletas de la ciudad</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C154" s="6" t="n">
-        <v>0.000408111934637182</v>
+        <v>0.0004093289682394798</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MO01CUX01 Apertura - BA Taxi</t>
+          <t>07. MO04CUX07 - Permitido estacionar</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C155" s="6" t="n">
-        <v>0.0004077062567697494</v>
+        <v>0.000408111934637182</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>INN10CUX02 Apertura - Experiencia trámites PI</t>
+          <t>MO01CUX01 Apertura - BA Taxi</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="C156" s="6" t="n">
-        <v>0.0004028381223605584</v>
+        <v>0.0004077062567697494</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EDU01CUX00 Superapertura Becas - Superapertura Becas</t>
+          <t>INN10CUX02 Apertura - Experiencia trámites PI</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="C157" s="6" t="n">
-        <v>0.0004008097330233954</v>
+        <v>0.0004028381223605584</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TR03CUX17 Permiso de carga excepcional (por viaje) - Desarrollo urbano y transporte - Transporte</t>
+          <t>EDU01CUX00 Superapertura Becas - Superapertura Becas</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
@@ -2589,638 +2589,638 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RC01CUX03 Apertura - Inscripción del Nacimiento</t>
+          <t>SUACI Componentes Comunes</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>935</v>
+        <v>948</v>
       </c>
       <c r="C165" s="6" t="n">
-        <v>0.0003793088060494683</v>
+        <v>0.000384582618326092</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EDU05CUX03 Apertura - Tecnicaturas</t>
+          <t>RC01CUX03 Apertura - Inscripción del Nacimiento</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>900</v>
+        <v>935</v>
       </c>
       <c r="C166" s="6" t="n">
-        <v>0.0003651100806893278</v>
+        <v>0.0003793088060494683</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EM01CUX02 Apertura - Violencia Laboral (DGNL)</t>
+          <t>EDU05CUX03 Apertura - Tecnicaturas</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C167" s="6" t="n">
-        <v>0.0003647044028218952</v>
+        <v>0.0003651100806893278</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SA07CUX01 Anticonceptivos - Salud Sexual y Reproductiva</t>
+          <t>EM01CUX02 Apertura - Violencia Laboral (DGNL)</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
-        <v>877</v>
+        <v>899</v>
       </c>
       <c r="C168" s="6" t="n">
-        <v>0.0003557794897383783</v>
+        <v>0.0003647044028218952</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CU01CUX02 Colón Fábrica - Museos</t>
+          <t>SA07CUX01 Anticonceptivos - Salud Sexual y Reproductiva</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C169" s="6" t="n">
-        <v>0.0003537511004012154</v>
+        <v>0.0003557794897383783</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TUR01CUX05 - Error - Turno para renovación de licencia de conducir</t>
+          <t>CU01CUX02 Colón Fábrica - Museos</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C170" s="6" t="n">
-        <v>0.0003480716102571592</v>
+        <v>0.0003488829659920244</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AC01CUX03 Gobierno Provincia Bs As - Gobierno de la Provincia</t>
+          <t>TUR01CUX05 - Error - Turno para renovación de licencia de conducir</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
-        <v>841</v>
+        <v>858</v>
       </c>
       <c r="C171" s="6" t="n">
-        <v>0.0003411750865108052</v>
+        <v>0.0003480716102571592</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt; ⏳ Espero [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>AC01CUX03 Gobierno Provincia Bs As - Gobierno de la Provincia</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="C172" s="6" t="n">
-        <v>0.0003375239857039119</v>
+        <v>0.0003411750865108052</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SUA01CUX11 Apertura - Extracción de árbol</t>
+          <t>Derivación a agente de SIGEHOS</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C173" s="6" t="n">
-        <v>0.0003371183078364794</v>
+        <v>0.0003375239857039119</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Viviendas SAP</t>
+          <t>SUA01CUX11 Apertura - Extracción de árbol</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C174" s="6" t="n">
-        <v>0.0003367126299690468</v>
+        <v>0.0003371183078364794</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Flow fulfilled of "Bifurcación para test" [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>Viviendas SAP</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C175" s="6" t="n">
-        <v>0.0003363069521016142</v>
+        <v>0.0003367126299690468</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CU01CUX06 Apertura - Buenos Aires Museo</t>
+          <t>Flow fulfilled of "Bifurcación para test" [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="C176" s="6" t="n">
-        <v>0.0003322501734272883</v>
+        <v>0.0003363069521016142</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SE01CUX03 Apertura - Agentes de prevención</t>
+          <t>CU01CUX06 Apertura - Buenos Aires Museo</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C177" s="6" t="n">
-        <v>0.0003314388176924231</v>
+        <v>0.0003322501734272883</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DDHH03CUX07 Apertura - Taller de espera activa</t>
+          <t>SE01CUX03 Apertura - Agentes de prevención</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="C178" s="6" t="n">
-        <v>0.0003277877168855299</v>
+        <v>0.0003314388176924231</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>07. MO04CUX07 - Permitido estacionar</t>
+          <t>DDHH03CUX07 Apertura - Taller de espera activa</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="C179" s="6" t="n">
-        <v>0.0003212968710066085</v>
+        <v>0.0003277877168855299</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>10. TR02CUX10 - Solicitud de Certificado de Legalidad (EX TRA04CUX01)</t>
+          <t>07. MO04CUX07 - Permitido estacionar</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C180" s="6" t="n">
-        <v>0.0003192684816694455</v>
+        <v>0.0003212968710066085</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SA02CUX03 Apertura - Certificado COVID-19</t>
+          <t>03. MO08CUX03 - AUSA - Sacar TelePASE</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C181" s="6" t="n">
-        <v>0.000318862803802013</v>
+        <v>0.0003212968710066085</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Deportes SAP</t>
+          <t>10. TR02CUX10 - Solicitud de Certificado de Legalidad (EX TRA04CUX01)</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c r="C182" s="6" t="n">
-        <v>0.0003139946693928219</v>
+        <v>0.0003192684816694455</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
+          <t>SA02CUX03 Apertura - Certificado COVID-19</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="C183" s="6" t="n">
-        <v>0.0003135889915253894</v>
+        <v>0.000318862803802013</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TR03CUX12 Apertura - Cementerios</t>
+          <t>Deportes SAP</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="C184" s="6" t="n">
-        <v>0.0003111549243207939</v>
+        <v>0.0003139946693928219</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SE02CUX04 Apertura - SAP Ciberseguridad</t>
+          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
-        <v>755</v>
+        <v>773</v>
       </c>
       <c r="C185" s="6" t="n">
-        <v>0.0003062867899116028</v>
+        <v>0.0003135889915253894</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MO05CUX04 Apertura - Pista de manejo</t>
+          <t>TR03CUX12 Apertura - Cementerios</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="C186" s="6" t="n">
-        <v>0.0003054754341767376</v>
+        <v>0.0003111549243207939</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>44. TR04CUX44 - Notificacion digital</t>
+          <t>SE02CUX04 Apertura - SAP Ciberseguridad</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C187" s="6" t="n">
-        <v>0.000305069756309305</v>
+        <v>0.0003062867899116028</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MO05CUX12 Apertura - Ampliación de licencias interjurisdiccional</t>
+          <t>MO05CUX04 Apertura - Pista de manejo</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C188" s="6" t="n">
-        <v>0.0003026356891047095</v>
+        <v>0.0003054754341767376</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>01. SA02CUX01 - Coronavirus</t>
+          <t>44. TR04CUX44 - Notificacion digital</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="C189" s="6" t="n">
-        <v>0.0003022300112372769</v>
+        <v>0.000305069756309305</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AGC02CUX01 Apertura - Ascensores</t>
+          <t>01. SA02CUX01 - Coronavirus</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="C190" s="6" t="n">
-        <v>0.000300201621900114</v>
+        <v>0.0003022300112372769</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>EP01CUX01 Apertura - BA Recicla</t>
+          <t>AGC02CUX01 Apertura - Ascensores</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="C191" s="6" t="n">
-        <v>0.0002912767088165971</v>
+        <v>0.000300201621900114</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CU02CUX02 Apertura corta - Teatro Colón</t>
+          <t>MO05CUX12 Apertura - Ampliación de licencias interjurisdiccional</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="C192" s="6" t="n">
-        <v>0.0002904653530817319</v>
+        <v>0.0002961448432257881</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AGC02CUX02 Director de Obra - Director de Obra</t>
+          <t>EP01CUX01 Apertura - BA Recicla</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="C193" s="6" t="n">
-        <v>0.0002847858629376757</v>
+        <v>0.0002912767088165971</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>33. TR04CUX33 - Permiso de espectáculos musicales en vivo</t>
+          <t>CU02CUX02 Apertura corta - Teatro Colón</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="C194" s="6" t="n">
-        <v>0.0002795120506610521</v>
+        <v>0.0002904653530817319</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DH09CUX01 Apertura - Desarrollo infantil</t>
+          <t>AGC02CUX02 Director de Obra - Director de Obra</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="C195" s="6" t="n">
-        <v>0.0002762666277215914</v>
+        <v>0.0002847858629376757</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DH10CUX01 Apertura - Trámites AFIP</t>
+          <t>33. TR04CUX33 - Permiso de espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="C196" s="6" t="n">
-        <v>0.0002758609498541588</v>
+        <v>0.0002795120506610521</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NI02CUX01 Superapertura - SAP de Niñez y Adolescencia</t>
+          <t>DH10CUX01 Apertura - Trámites AFIP</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="C197" s="6" t="n">
-        <v>0.0002754552719867262</v>
+        <v>0.0002782950170587543</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SUA01CUX21 Apertura - Reubicación de contenedores</t>
+          <t>DH09CUX01 Apertura - Desarrollo infantil</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="C198" s="6" t="n">
-        <v>0.0002726155269146981</v>
+        <v>0.0002762666277215914</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TR03CUX20 Apertura - Dirección general de ferias</t>
+          <t>NI02CUX01 Superapertura - SAP de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="C199" s="6" t="n">
-        <v>0.0002726155269146981</v>
+        <v>0.0002754552719867262</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt; ✅ Operador disponible [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>SUA01CUX21 Apertura - Reubicación de contenedores</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C200" s="6" t="n">
-        <v>0.0002713984933124004</v>
+        <v>0.0002726155269146981</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RC01CUX06 Apertura - Autorización Viaje al exterior y nacional</t>
+          <t>TR03CUX20 Apertura - Dirección general de ferias</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="C201" s="6" t="n">
-        <v>0.0002685587482403722</v>
+        <v>0.0002726155269146981</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CU09CUX01 CCK - Centros culturales</t>
+          <t>Derivación a agente de SIGEHOS</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="C202" s="6" t="n">
-        <v>0.0002657190031683441</v>
+        <v>0.0002713984933124004</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EM03CUX01 Apertura - Empleo Joven</t>
+          <t>RC01CUX06 Apertura - Autorización Viaje al exterior y nacional</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="C203" s="6" t="n">
-        <v>0.0002636906138311812</v>
+        <v>0.0002685587482403722</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>38. TR04CUX38 - Consulta de Expedientes Electrónicos | Trámites STD</t>
+          <t>EM03CUX01 Apertura - Empleo Joven</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
-        <v>631</v>
+        <v>650</v>
       </c>
       <c r="C204" s="6" t="n">
-        <v>0.0002559827343499621</v>
+        <v>0.0002636906138311812</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DEC05CUX01 Apertura - Boti para empresas, SAP</t>
+          <t>CU09CUX01 CCK - Centros culturales</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C205" s="6" t="n">
-        <v>0.000253142989277934</v>
+        <v>0.0002563884122173946</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>04. SA02CUX04 - Hisopado COVID-19 - Consulta y resultado</t>
+          <t>38. TR04CUX38 - Consulta de Expedientes Electrónicos | Trámites STD</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="C206" s="6" t="n">
-        <v>0.0002515202778082036</v>
+        <v>0.0002559827343499621</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TR02CUX12 Cómo es el trámite - Solicitud Partida de Matrimonio</t>
+          <t>DEC05CUX01 Apertura - Boti para empresas, SAP</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C207" s="6" t="n">
-        <v>0.0002507089220733385</v>
+        <v>0.000253142989277934</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CU02CUX01 Apertura - Teatros</t>
+          <t>04. SA02CUX04 - Hisopado COVID-19 - Consulta y resultado</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="C208" s="6" t="n">
-        <v>0.0002470578212664452</v>
+        <v>0.0002515202778082036</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>03. MO08CUX03 - AUSA - Sacar TelePASE</t>
+          <t>TR02CUX12 Cómo es el trámite - Solicitud Partida de Matrimonio</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="C209" s="6" t="n">
-        <v>0.0002446237540618497</v>
+        <v>0.0002507089220733385</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AC02CUX04 Teléfonos Emergencias - Emergencias</t>
+          <t>CU02CUX01 Apertura - Teatros</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>591</v>
+        <v>609</v>
       </c>
       <c r="C210" s="6" t="n">
-        <v>0.0002397556196526586</v>
+        <v>0.0002470578212664452</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>INN10CUX12 Preapertura - Servicios Sociales</t>
+          <t>AC02CUX04 Teléfonos Emergencias - Emergencias</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C211" s="6" t="n">
-        <v>0.0002365101967131979</v>
+        <v>0.0002397556196526586</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GA02CUX01 Apertura - Ferias de la Ciudad</t>
+          <t>INN10CUX12 Preapertura - Servicios Sociales</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C212" s="6" t="n">
-        <v>0.0002356988409783327</v>
+        <v>0.0002365101967131979</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CO12CUX01 Apertura - Cortes de Luz</t>
+          <t>GA02CUX01 Apertura - Ferias de la Ciudad</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="C213" s="6" t="n">
-        <v>0.0002292079950994114</v>
+        <v>0.0002356988409783327</v>
       </c>
     </row>
     <row r="214">
@@ -3239,20 +3239,20 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Género [GE] [GE03CUX01 Super Apertura]</t>
+          <t>CO12CUX01 Apertura - Cortes de Luz</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C215" s="6" t="n">
-        <v>0.0002263682500273832</v>
+        <v>0.0002292079950994114</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CIU06CUX03 Apertura de Contingencia - Equipo BA</t>
+          <t>Género [GE] [GE03CUX01 Super Apertura]</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
@@ -3265,137 +3265,137 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>AGC01CUX01  Apertura - Habilitaciones</t>
+          <t>CIU06CUX03 Apertura de Contingencia - Equipo BA</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C217" s="6" t="n">
-        <v>0.0002239341828227877</v>
+        <v>0.0002263682500273832</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CIU05CUX07 Apertura QR - Barrio Mugica</t>
+          <t>AGC01CUX01  Apertura - Habilitaciones</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C218" s="6" t="n">
-        <v>0.0002202830820158944</v>
+        <v>0.0002239341828227877</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TR02CUX06 - Apertura - Presentación de Certificados Escolares para Estudiar es Trabajar -</t>
+          <t>TR03CUX28 Trámites por venta de vehículo ante la Dirección Nacional de los Registros Nacionales de la Propiedad del Automotor y Créditos Prendarios - Nación</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C219" s="6" t="n">
-        <v>0.0002194717262810293</v>
+        <v>0.0002206887598833271</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DDHH03CUX08 Apertura - Derivación Línea 102</t>
+          <t>CIU05CUX07 Apertura QR - Barrio Mugica</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C220" s="6" t="n">
-        <v>0.0002174433369438664</v>
+        <v>0.0002202830820158944</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SUA01CUX19 Apertura - Desagote pozo ciego</t>
+          <t>TR02CUX06 - Apertura - Presentación de Certificados Escolares para Estudiar es Trabajar -</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C221" s="6" t="n">
-        <v>0.0002146035918718382</v>
+        <v>0.0002194717262810293</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>COY08CUX01 Apertura - Obras en la ciudad</t>
+          <t>Línea 102</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="C222" s="6" t="n">
-        <v>0.000210952491064945</v>
+        <v>0.0002174433369438664</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TR03CUX28 Trámites por venta de vehículo ante la Dirección Nacional de los Registros Nacionales de la Propiedad del Automotor y Créditos Prendarios - Nación</t>
+          <t>SUA01CUX19 Apertura - Desagote pozo ciego</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="C223" s="6" t="n">
-        <v>0.0002068957123906191</v>
+        <v>0.0002146035918718382</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SUA01CUX14 Apertura - Reparación de Baches</t>
+          <t>COY08CUX01 Apertura - Obras en la ciudad</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="C224" s="6" t="n">
-        <v>0.0002068957123906191</v>
+        <v>0.000210952491064945</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EDU05CUX01 Apertura - Beneficios para universitarios</t>
+          <t>SUA01CUX14 Apertura - Reparación de Baches</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C225" s="6" t="n">
-        <v>0.0002064900345231865</v>
+        <v>0.0002068957123906191</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EDU04CUX06 Apertura - Bullying</t>
+          <t>EDU05CUX01 Apertura - Beneficios para universitarios</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C226" s="6" t="n">
-        <v>0.0002056786787883213</v>
+        <v>0.0002064900345231865</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GE01CUX02 Apertura - Violencia contra la mujer</t>
+          <t>EDU04CUX06 Apertura - Bullying</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -3408,124 +3408,124 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CU09CUX02 Apertura - Cementerios de Buenos Aires</t>
+          <t>GE01CUX02 Apertura - Violencia contra la mujer</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C228" s="6" t="n">
-        <v>0.0002044616451860236</v>
+        <v>0.0002056786787883213</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CU13CUX01 Apertura - Patrimonio de la Ciudad</t>
+          <t>TR04CUX41 Antecedentes penales - Trámites Nación</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C229" s="6" t="n">
-        <v>0.0002044616451860236</v>
+        <v>0.0002052730009208888</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DE04CUX01 Apertura - Polideportivos</t>
+          <t>CU13CUX01 Apertura - Patrimonio de la Ciudad</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C230" s="6" t="n">
-        <v>0.000204055967318591</v>
+        <v>0.0002044616451860236</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SUACI Componentes Comunes</t>
+          <t>CU09CUX02 Apertura - Cementerios de Buenos Aires</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C231" s="6" t="n">
-        <v>0.0002028389337162932</v>
+        <v>0.0002044616451860236</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AGC01CUX02  Apertura - Inspecciones</t>
+          <t>DE04CUX01 Apertura - Polideportivos</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C232" s="6" t="n">
-        <v>0.0002028389337162932</v>
+        <v>0.000204055967318591</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CU04CUX01 Apertura - Feria del libro 2026</t>
+          <t>AGC01CUX02  Apertura - Inspecciones</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C233" s="6" t="n">
-        <v>0.0001983764771745348</v>
+        <v>0.0002028389337162932</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TR04CUX32  Apertura - Pasaporte</t>
+          <t>TUR01CUX05 Pago de BUI - Turno para renovación de licencia de conducir</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C234" s="6" t="n">
-        <v>0.0001979707993071022</v>
+        <v>0.0001999991886442651</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EDU04CUX25 Apertura - Plan Sarmiento</t>
+          <t>CU04CUX01 Apertura - Feria del libro 2026</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C235" s="6" t="n">
-        <v>0.0001951310542350741</v>
+        <v>0.0001983764771745348</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TR04CUX41 Antecedentes penales - Trámites Nación</t>
+          <t>EDU04CUX25 Apertura - Plan Sarmiento</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C236" s="6" t="n">
-        <v>0.0001939140206327763</v>
+        <v>0.0001951310542350741</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SUA01CUX34 Vaciado de contenedor - Vaciado de contenedor</t>
+          <t>DH07CUX02 SAP Inclusión Laboral - SAP Inclusión Laboral</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
@@ -3538,7 +3538,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DH07CUX02 SAP Inclusión Laboral - SAP Inclusión Laboral</t>
+          <t>SUA01CUX34 Vaciado de contenedor - Vaciado de contenedor</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
@@ -3616,14 +3616,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TR04CUX31 Cómo lo hago - Legalización de Títulos</t>
+          <t>TR04CUX32  Apertura - Pasaporte</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C244" s="6" t="n">
-        <v>0.0001849891075492594</v>
+        <v>0.0001858004632841246</v>
       </c>
     </row>
     <row r="245">
@@ -3707,358 +3707,358 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>AGC [AGC] [AGC01CUX00  Apertura]</t>
+          <t>TR04CUX31 Cómo lo hago - Legalización de Títulos</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C251" s="6" t="n">
-        <v>0.0001772812280680403</v>
+        <v>0.0001776869059354729</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CO12CUX02 Temporal en BA - Temporal en BA</t>
+          <t>AGC [AGC] [AGC01CUX00  Apertura]</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C252" s="6" t="n">
-        <v>0.0001748471608634448</v>
+        <v>0.0001772812280680403</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>40. TR04CUX40 - Solicitud de Copia Digital de Expediente y/o Documento | Trámites STD</t>
+          <t>CO12CUX02 Temporal en BA - Temporal en BA</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C253" s="6" t="n">
-        <v>0.000173630127261147</v>
+        <v>0.0001752528387308773</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>DH08CUX01 Apertura - Cursos de educación financiera</t>
+          <t>o Documento | Trámites STD</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C254" s="6" t="n">
-        <v>0.0001732244493937144</v>
+        <v>0.000173630127261147</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SUA01CUX25 Apertura - Reparación de contenedores</t>
+          <t>DH08CUX01 Apertura - Cursos de educación financiera</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C255" s="6" t="n">
-        <v>0.0001695733485868211</v>
+        <v>0.0001732244493937144</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SA02CUX01 Evaluación COVID-19 - Coronavirus</t>
+          <t>SUA01CUX25 Apertura - Reparación de contenedores</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C256" s="6" t="n">
-        <v>0.0001683563149845234</v>
+        <v>0.0001695733485868211</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>01. EM04CUX01 - BA PyMES y BA Empresas</t>
+          <t>SA02CUX01 Evaluación COVID-19 - Coronavirus</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C257" s="6" t="n">
-        <v>0.0001671392813822256</v>
+        <v>0.0001683563149845234</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CIU05CUX12 Apertura de encuesta - Agentes en Calle</t>
+          <t>01. EM04CUX01 - BA PyMES y BA Empresas</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C258" s="6" t="n">
-        <v>0.0001638938584427649</v>
+        <v>0.0001671392813822256</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SA14CUX01 Apertura - Prevención cáncer de mama</t>
+          <t>CIU05CUX12 Apertura de encuesta - Agentes en Calle</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C259" s="6" t="n">
-        <v>0.0001634881805753323</v>
+        <v>0.0001638938584427649</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CO10CUX02 Apertura post evento - | Voto en la Ciudad</t>
+          <t>SA14CUX01 Apertura - Prevención cáncer de mama</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C260" s="6" t="n">
-        <v>0.0001622711469730346</v>
+        <v>0.0001634881805753323</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SUA01CUX29 Apertura columnas en mal estado - Poste en mal estado</t>
+          <t>CO10CUX02 Apertura post evento - | Voto en la Ciudad</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C261" s="6" t="n">
-        <v>0.0001602427576358717</v>
+        <v>0.0001622711469730346</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SIGEHOS &gt;❌ Fuera de Horario [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>SUA01CUX29 Apertura columnas en mal estado - Poste en mal estado</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C262" s="6" t="n">
-        <v>0.0001598370797684391</v>
+        <v>0.0001602427576358717</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CU06CUX03 Apertura - Identidad de género ??????</t>
+          <t>Derivación a agente de SIGEHOS</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C263" s="6" t="n">
-        <v>0.0001586200461661413</v>
+        <v>0.0001590257240335739</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SUA01CUX13 Apertura - Falta de conservación de fachada</t>
+          <t>CU06CUX03 Apertura - Identidad de género 🏳️‍⚧️</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C264" s="6" t="n">
-        <v>0.0001574030125638435</v>
+        <v>0.0001586200461661413</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MO02CUX01 Apertura - Servicio de Cercanía</t>
+          <t>SUA01CUX13 Apertura - Falta de conservación de fachada</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C265" s="6" t="n">
-        <v>0.0001565916568289784</v>
+        <v>0.0001574030125638435</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TUR01CUX11 Sacar turno - Turno para práctica de auto en pista</t>
+          <t>MO02CUX01 Apertura - Servicio de Cercanía</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C266" s="6" t="n">
-        <v>0.0001529405560220851</v>
+        <v>0.0001553746232266806</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>VI01CUX01 Apertura - Programa Viviendas IVC</t>
+          <t>TR03CUX03 Proescritores - Cultura</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C267" s="6" t="n">
-        <v>0.0001521292002872199</v>
+        <v>0.0001545632674918155</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TR03CUX03 Proescritores - Cultura</t>
+          <t>CIU05CUX09 Parque Rivadavia - Caballito</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C268" s="6" t="n">
-        <v>0.0001509121666849222</v>
+        <v>0.0001541575896243829</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SUA01CUX17 Apertura - Pintura sobre Graffiti</t>
+          <t>TUR01CUX11 Sacar turno - Turno para práctica de auto en pista</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C269" s="6" t="n">
-        <v>0.0001509121666849222</v>
+        <v>0.0001529405560220851</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CIU05CUX09 Parque Rivadavia - Caballito</t>
+          <t>VI01CUX01 Apertura - Programa Viviendas IVC</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C270" s="6" t="n">
-        <v>0.0001472610658780289</v>
+        <v>0.0001521292002872199</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>EDU03CUX09 Apertura - Tramitación Designaciones Interinas</t>
+          <t>SUA01CUX17 Apertura - Pintura sobre Graffiti</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C271" s="6" t="n">
-        <v>0.0001472610658780289</v>
+        <v>0.0001509121666849222</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CIU02CUX01 Apertura - Comunas de la Ciudad</t>
+          <t>EDU03CUX09 Apertura - Tramitación Designaciones Interinas</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C272" s="6" t="n">
-        <v>0.0001464497101431637</v>
+        <v>0.0001472610658780289</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>VI01CUX02 Apertura - Garantía + Fácil</t>
+          <t>CIU02CUX01 Sedes comunales - Comunas de la Ciudad</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C273" s="6" t="n">
-        <v>0.0001423929314688379</v>
+        <v>0.0001468553880105963</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Solicitudes - Suaci [SUACI] [SUA01CUX00 Apertura corta]</t>
+          <t>VI01CUX02 Apertura - Garantía + Fácil</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C274" s="6" t="n">
-        <v>0.0001415815757339727</v>
+        <v>0.0001423929314688379</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CIU02CUX01 Sedes comunales - Comunas de la Ciudad</t>
+          <t>Solicitudes - Suaci [SUACI] [SUA01CUX00 Apertura corta]</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C275" s="6" t="n">
-        <v>0.0001407702199991075</v>
+        <v>0.0001415815757339727</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TR01CUX10 Apertura - Copia de Plano</t>
+          <t>CIU02CUX01 Apertura - Comunas de la Ciudad</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C276" s="6" t="n">
-        <v>0.0001399588642642423</v>
+        <v>0.0001403645421316749</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Instancias de espera AGIP</t>
+          <t>TR01CUX10 Apertura - Copia de Plano</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C277" s="6" t="n">
-        <v>0.0001395531863968097</v>
+        <v>0.0001399588642642423</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TR02CUX13 Cómo es el trámite - Solicitud de Partida de defunción</t>
+          <t>Instancias de espera AGIP</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -4084,7 +4084,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CU09CUX04 Apertura - Jardín Japonés</t>
+          <t>SA10CUX03 Mapa de Salud - Mapa de salud</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -4097,7 +4097,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>SA10CUX03 Mapa de Salud - Mapa de salud</t>
+          <t>15. EDU04CUX15 - Escuelas públicas bilingües</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -4110,27 +4110,27 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>15. EDU04CUX15 - Escuelas públicas bilingües</t>
+          <t>CU09CUX04 Apertura - Jardín Japonés</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C282" s="6" t="n">
-        <v>0.0001367134413247817</v>
+        <v>0.0001375247970596468</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TR03CUX17 Reserva de espacio para estacionamiento de vehículos de personas con discapacidad - Desarrollo urbano y transporte - Transporte</t>
+          <t>TR02CUX13 Cómo es el trámite - Solicitud de Partida de defunción</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C283" s="6" t="n">
-        <v>0.0001350907298550513</v>
+        <v>0.0001363077634573491</v>
       </c>
     </row>
     <row r="284">
@@ -4214,124 +4214,124 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TR01CUX05 Apertura - Actualización, Rectificación y/o Modificación de datos Registro de Empleadores</t>
+          <t>EDU04CUX26 Apertura web - Preinscripción escolar</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C290" s="6" t="n">
-        <v>0.0001273828503738322</v>
+        <v>0.0001298169175784277</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SUA01CUX36 Reparación de semaforo - Reparación de semáforo</t>
+          <t>o Modificación de datos Registro de Empleadores</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C291" s="6" t="n">
-        <v>0.0001261658167715344</v>
+        <v>0.0001273828503738322</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>EDU04CUX26 Apertura web - Preinscripción escolar</t>
+          <t>SUA01CUX36 Reparación de semaforo - Reparación de semáforo</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C292" s="6" t="n">
-        <v>0.0001257601389041018</v>
+        <v>0.0001261658167715344</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MO06CUX02 Apertura - Ecobici</t>
+          <t>TR03CUX17 Reserva de espacio para estacionamiento de vehículos de personas con discapacidad - Desarrollo urbano y transporte - Transporte</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C293" s="6" t="n">
-        <v>0.0001249487831692366</v>
+        <v>0.0001261658167715344</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>EDU09CUX01 Apertura - Educación ambiental</t>
+          <t>MO06CUX02 Apertura - Ecobici</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C294" s="6" t="n">
-        <v>0.0001245431053018041</v>
+        <v>0.0001249487831692366</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TR02CUX01 Apertura - Solicitud de Certificado de Deudor Alimentario |</t>
+          <t>EDU09CUX01 Apertura - Educación ambiental</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C295" s="6" t="n">
-        <v>0.0001237317495669389</v>
+        <v>0.0001245431053018041</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>PC03CUX01 Apertura - Participación ciudadana</t>
+          <t>TR02CUX01 Apertura - Solicitud de Certificado de Deudor Alimentario |</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C296" s="6" t="n">
-        <v>0.0001229203938320737</v>
+        <v>0.0001237317495669389</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SE02CUX01 Apertura - Ciberestafas</t>
+          <t>PC03CUX01 Apertura - Participación ciudadana</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C297" s="6" t="n">
-        <v>0.0001225147159646411</v>
+        <v>0.0001229203938320737</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TR04CUX07 Apertura - ANSES</t>
+          <t>SE02CUX01 Apertura - Ciberestafas</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C298" s="6" t="n">
-        <v>0.0001221090380972085</v>
+        <v>0.0001225147159646411</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>DE05CUX01 Apertura - Clases al aire libre</t>
+          <t>TR04CUX07 Apertura - ANSES</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -4344,144 +4344,144 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>EDU05CUX06 Apertura - Profesorados</t>
+          <t>DE05CUX01 Apertura - Clases al aire libre</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C300" s="6" t="n">
-        <v>0.0001208920044949108</v>
+        <v>0.0001221090380972085</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TR01CUX06 Apertura - Adecuación Provisoria Redeterminación de Precios</t>
+          <t>EDU05CUX06 Apertura - Profesorados</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C301" s="6" t="n">
-        <v>0.0001208920044949108</v>
+        <v>0.000121703360229776</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>DH01CUX04 Pregunta 1 - Encuesta Subsidio Habitacional 690</t>
+          <t>TR03CUX16 Consorcios - Defensa del consumidor</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C302" s="6" t="n">
-        <v>0.0001204863266274782</v>
+        <v>0.0001212976823623434</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10. TR04CUX10 - Boletín oficial y Sindicatura General</t>
+          <t>TR01CUX06 Apertura - Adecuación Provisoria Redeterminación de Precios</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C303" s="6" t="n">
-        <v>0.0001204863266274782</v>
+        <v>0.0001208920044949108</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>02. DE05CUX02 - Deportes en barrios</t>
+          <t>10. TR04CUX10 - Boletín oficial y Sindicatura General</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C304" s="6" t="n">
-        <v>0.0001188636151577478</v>
+        <v>0.0001204863266274782</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>GE01CUX03 Apertura - Acoso callejero</t>
+          <t>DH01CUX04 Pregunta 1 - Encuesta Subsidio Habitacional 690</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C305" s="6" t="n">
-        <v>0.0001180522594228827</v>
+        <v>0.0001204863266274782</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EDU01CUX03 Apertura - Becas Grierson</t>
+          <t>02. DE05CUX02 - Deportes en barrios</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C306" s="6" t="n">
-        <v>0.0001168352258205849</v>
+        <v>0.0001188636151577478</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>TR03CUX16 Consorcios - Defensa del consumidor</t>
+          <t>GE01CUX03 Apertura - Acoso callejero</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C307" s="6" t="n">
-        <v>0.0001160238700857197</v>
+        <v>0.0001180522594228827</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EDU01CUX02 Apertura - Becas Nivel Superior</t>
+          <t>EDU01CUX03 Apertura - Becas Grierson</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C308" s="6" t="n">
-        <v>0.000114806836483422</v>
+        <v>0.0001168352258205849</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TR03CUX28 CUIL - Nación</t>
+          <t>EDU01CUX02 Apertura - Becas Nivel Superior</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C309" s="6" t="n">
-        <v>0.0001135898028811242</v>
+        <v>0.000114806836483422</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CIU04CUX01 Apertura - Estadisticas y Censos</t>
+          <t>TR03CUX09 Ruidos molestos provenientes de actividades comerciales e industriales - Ambiente y EP</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C310" s="6" t="n">
-        <v>0.0001131841250136916</v>
+        <v>0.0001139954807485568</v>
       </c>
     </row>
     <row r="311">
@@ -4500,20 +4500,20 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>DH03CUX03 Apertura - Autismo</t>
+          <t>CIU04CUX01 Apertura - Estadisticas y Censos</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C312" s="6" t="n">
-        <v>0.000112778447146259</v>
+        <v>0.0001131841250136916</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>TR03CUX09 Ruidos molestos provenientes de actividades comerciales e industriales - Ambiente y EP</t>
+          <t>DH03CUX03 Apertura - Autismo</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
@@ -4539,85 +4539,85 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>21. TR01CUX21 |Apertura TAD</t>
+          <t>DH04CUX05 Apertura - Fiscalizadores de Residencias Geriátricas</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C315" s="6" t="n">
-        <v>0.0001111557356765287</v>
+        <v>0.0001107500578090961</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>DH04CUX05 Apertura - Fiscalizadores de Residencias Geriátricas</t>
+          <t>JU01CUX01 Apertura - Servicios Jurídicos Gratuitos</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C316" s="6" t="n">
-        <v>0.0001107500578090961</v>
+        <v>0.0001070989570022028</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>JU01CUX01 Apertura - Servicios Jurídicos Gratuitos</t>
+          <t>GA03CUX10 Apertura - Comunidad MAPPA</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C317" s="6" t="n">
-        <v>0.0001070989570022028</v>
+        <v>0.0001058819233999051</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>GA03CUX10 Apertura - Comunidad MAPPA</t>
+          <t>21. TR01CUX21 |Apertura TAD</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C318" s="6" t="n">
-        <v>0.0001058819233999051</v>
+        <v>0.0001042592119301747</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>DH09CUX02 Apertura - Programa Adolescencia</t>
+          <t>TR03CUX05 Apertura - Ministerio de Educación e Innovación - Otros trámites</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C319" s="6" t="n">
-        <v>0.0001014194668581466</v>
+        <v>0.0001018251447255792</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>TR03CUX05 Apertura - Ministerio de Educación e Innovación - Otros trámites</t>
+          <t>DH09CUX02 Apertura - Programa Adolescencia</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C320" s="6" t="n">
-        <v>0.000101013788990714</v>
+        <v>0.0001014194668581466</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>01. SUA02CUX01 - Estado de trámites y solicitudes</t>
+          <t>TR01CUX08 Apertura - Certificación Documentación Institución Activa</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
@@ -4630,14 +4630,14 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>TR01CUX08 Apertura - Certificación Documentación Institución Activa</t>
+          <t>01. SUA02CUX01 - Estado de trámites y solicitudes</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C322" s="6" t="n">
-        <v>0.0001002024332558489</v>
+        <v>0.0001006081111232814</v>
       </c>
     </row>
     <row r="323">
@@ -4695,7 +4695,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CU01CUX01 Apertura - Usina del Arte</t>
+          <t>EDU10CUX01 Ayuda cuota escolar - Ayuda cuota escolar</t>
         </is>
       </c>
       <c r="B327" s="5" t="n">
@@ -4708,7 +4708,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>EDU10CUX01 Ayuda cuota escolar - Ayuda cuota escolar</t>
+          <t>CU01CUX01 Apertura - Usina del Arte</t>
         </is>
       </c>
       <c r="B328" s="5" t="n">
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="B332" s="5" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C332" s="6" t="n">
-        <v>9.29002316420623e-05</v>
+        <v>9.330590950949489e-05</v>
       </c>
     </row>
     <row r="333">
@@ -4799,27 +4799,27 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Test [Test IABA Feedback by options]</t>
+          <t>TR03CUX28 CUIL - Nación</t>
         </is>
       </c>
       <c r="B335" s="5" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C335" s="6" t="n">
-        <v>8.843777510030385e-05</v>
+        <v>9.00604865700342e-05</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CU10CUX01 Apertura - Casco Histórico</t>
+          <t>Test [Test IABA Feedback by options]</t>
         </is>
       </c>
       <c r="B336" s="5" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C336" s="6" t="n">
-        <v>8.600370789570833e-05</v>
+        <v>8.843777510030385e-05</v>
       </c>
     </row>
     <row r="337">
@@ -4838,20 +4838,20 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>TUR01CUX05 Pago de BUI - Turno para renovación de licencia de conducir</t>
+          <t>CU10CUX01 Apertura - Casco Histórico</t>
         </is>
       </c>
       <c r="B338" s="5" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C338" s="6" t="n">
-        <v>8.478667429341057e-05</v>
+        <v>8.600370789570833e-05</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TR02CUX13 Partida de defunción SD - Solicitud de Partida de defunción</t>
+          <t>TR02CUX05 - Apertura - Entrega de Certificados Escolares para Ciudadanía Porteña-</t>
         </is>
       </c>
       <c r="B339" s="5" t="n">
@@ -4864,53 +4864,53 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CU01CUX14 Apertura Estático - MIJU</t>
+          <t>TR04CUX32  Primer pasaporte - Pasaporte</t>
         </is>
       </c>
       <c r="B340" s="5" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C340" s="6" t="n">
-        <v>8.438099642597798e-05</v>
+        <v>8.39753185585454e-05</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>TR02CUX05 - Apertura - Entrega de Certificados Escolares para Ciudadanía Porteña-</t>
+          <t>SA13CUX01 Apertura - Cursos RCP y Primeros Auxilios</t>
         </is>
       </c>
       <c r="B341" s="5" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C341" s="6" t="n">
-        <v>8.39753185585454e-05</v>
+        <v>8.356964069111282e-05</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>SA13CUX01 Apertura - Cursos RCP y Primeros Auxilios</t>
+          <t>CU11CUX02 Apertura - Programa Cultural en Barrios</t>
         </is>
       </c>
       <c r="B342" s="5" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C342" s="6" t="n">
-        <v>8.356964069111282e-05</v>
+        <v>8.316396282368023e-05</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CU11CUX02 Apertura - Programa Cultural en Barrios</t>
+          <t>CU01CUX14 Apertura Estático - MIJU</t>
         </is>
       </c>
       <c r="B343" s="5" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C343" s="6" t="n">
-        <v>8.316396282368023e-05</v>
+        <v>8.275828495624764e-05</v>
       </c>
     </row>
     <row r="344">
@@ -4955,14 +4955,14 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>03. TR02CUX03 VI01CUX03 - Copia de escritura</t>
+          <t>TR02CUX13 Partida de defunción SD - Solicitud de Partida de defunción</t>
         </is>
       </c>
       <c r="B347" s="5" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C347" s="6" t="n">
-        <v>8.032421775165212e-05</v>
+        <v>8.072989561908471e-05</v>
       </c>
     </row>
     <row r="348">
@@ -4981,189 +4981,189 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>01. BOT01CUX01 - Personalidad</t>
+          <t>03. TR02CUX03 VI01CUX03 - Copia de escritura</t>
         </is>
       </c>
       <c r="B349" s="5" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C349" s="6" t="n">
-        <v>7.748447267962402e-05</v>
+        <v>8.032421775165212e-05</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>EDU03CUX05  Apertura - Universidad de la Ciudad</t>
+          <t>CU09CUX01 Apertura - Centros culturales</t>
         </is>
       </c>
       <c r="B350" s="5" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C350" s="6" t="n">
-        <v>7.707879481219143e-05</v>
+        <v>7.870150628192177e-05</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>AC02CUX02 Apertura - Protección ambiental</t>
+          <t>TR03CUX08 Apertura - AGC</t>
         </is>
       </c>
       <c r="B351" s="5" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C351" s="6" t="n">
-        <v>7.667311694475884e-05</v>
+        <v>7.789015054705661e-05</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>TR03CUX08 Apertura - AGC</t>
+          <t>01. BOT01CUX01 - Personalidad</t>
         </is>
       </c>
       <c r="B352" s="5" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C352" s="6" t="n">
-        <v>7.423904974016333e-05</v>
+        <v>7.748447267962402e-05</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>TR04CUX08 Asiento de la defunción en la libreta de matrimonio - Asiento de la defunción en la libreta de matrimonio</t>
+          <t>EDU03CUX05  Apertura - Universidad de la Ciudad</t>
         </is>
       </c>
       <c r="B353" s="5" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C353" s="6" t="n">
-        <v>7.423904974016333e-05</v>
+        <v>7.707879481219143e-05</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>20. TR04CUX20 - Dirección General de Mesa de Entradas, Salidas y Archivo</t>
+          <t>AC02CUX02 Apertura - Protección ambiental</t>
         </is>
       </c>
       <c r="B354" s="5" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C354" s="6" t="n">
-        <v>7.423904974016333e-05</v>
+        <v>7.667311694475884e-05</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>TR04CUX32  Primer pasaporte - Pasaporte</t>
+          <t>TR04CUX31 Qué necesito - Legalización de Títulos</t>
         </is>
       </c>
       <c r="B355" s="5" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C355" s="6" t="n">
-        <v>7.18049825355678e-05</v>
+        <v>7.545608334246108e-05</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>DDHH01CUX01 Apertura - Guía Migrante</t>
+          <t>20. TR04CUX20 - Dirección General de Mesa de Entradas, Salidas y Archivo</t>
         </is>
       </c>
       <c r="B356" s="5" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C356" s="6" t="n">
-        <v>7.139930466813521e-05</v>
+        <v>7.423904974016333e-05</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>06. Programa de acogimiento familiar</t>
+          <t>TR04CUX08 Asiento de la defunción en la libreta de matrimonio - Asiento de la defunción en la libreta de matrimonio</t>
         </is>
       </c>
       <c r="B357" s="5" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C357" s="6" t="n">
-        <v>7.139930466813521e-05</v>
+        <v>7.423904974016333e-05</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>02. RC01CUX02 - Información sumaria testimonial de Declaración de domicilio</t>
+          <t>06. Programa de acogimiento familiar</t>
         </is>
       </c>
       <c r="B358" s="5" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C358" s="6" t="n">
-        <v>7.058794893327005e-05</v>
+        <v>7.139930466813521e-05</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CU09CUX01 Apertura - Centros culturales</t>
+          <t>02. RC01CUX02 - Información sumaria testimonial de Declaración de domicilio</t>
         </is>
       </c>
       <c r="B359" s="5" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C359" s="6" t="n">
-        <v>6.937091533097229e-05</v>
+        <v>7.058794893327005e-05</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>18. EDU04CUX18 Apoyo Escolar</t>
+          <t>DDHH01CUX01 Apertura - Guía Migrante</t>
         </is>
       </c>
       <c r="B360" s="5" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C360" s="6" t="n">
-        <v>6.937091533097229e-05</v>
+        <v>7.058794893327005e-05</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>TR04CUX31 Qué necesito - Legalización de Títulos</t>
+          <t>Mensaje por defecto [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B361" s="5" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C361" s="6" t="n">
-        <v>6.815388172867453e-05</v>
+        <v>7.058794893327005e-05</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Mensaje por defecto [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>18. EDU04CUX18 Apoyo Escolar</t>
         </is>
       </c>
       <c r="B362" s="5" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C362" s="6" t="n">
-        <v>6.815388172867453e-05</v>
+        <v>6.937091533097229e-05</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>VI03CUX01 Apertura - Créditos Hipotecarios</t>
+          <t>CU09CUX03 Apertura - Palacio Barolo</t>
         </is>
       </c>
       <c r="B363" s="5" t="n">
@@ -5176,7 +5176,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>INN09CUX01 Apertura - Firma digital</t>
+          <t>TUR01CUX12 Preguntar género - Turno para infracciones por videollamada</t>
         </is>
       </c>
       <c r="B364" s="5" t="n">
@@ -5189,14 +5189,14 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CU09CUX03 Apertura - Palacio Barolo</t>
+          <t>INN09CUX01 Apertura - Firma digital</t>
         </is>
       </c>
       <c r="B365" s="5" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C365" s="6" t="n">
-        <v>6.653117025894418e-05</v>
+        <v>6.612549239151159e-05</v>
       </c>
     </row>
     <row r="366">
@@ -5215,14 +5215,14 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>TUR01CUX12 Preguntar género - Turno para infracciones por videollamada</t>
+          <t>VI03CUX01 Apertura - Créditos Hipotecarios</t>
         </is>
       </c>
       <c r="B367" s="5" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C367" s="6" t="n">
-        <v>6.531413665664643e-05</v>
+        <v>6.409710305434866e-05</v>
       </c>
     </row>
     <row r="368">
@@ -5254,7 +5254,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>INN10CUX09 Apertura - Experiencia accesibilidad PI</t>
+          <t>SE02CUX02 Apertura - Internet segura</t>
         </is>
       </c>
       <c r="B370" s="5" t="n">
@@ -5267,20 +5267,20 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>SE02CUX02 Apertura - Internet segura</t>
+          <t>SUA01CUX01 Apertura - Criadero de mosquitos</t>
         </is>
       </c>
       <c r="B371" s="5" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C371" s="6" t="n">
-        <v>6.28800694520509e-05</v>
+        <v>6.247439158461831e-05</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SUA01CUX01 Apertura - Criadero de mosquitos</t>
+          <t>MO04CUX10 Apertura - Accidentes de tránsito</t>
         </is>
       </c>
       <c r="B372" s="5" t="n">
@@ -5293,79 +5293,79 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>MO04CUX10 Apertura - Accidentes de tránsito</t>
+          <t>TR02CUX10 Confirmar trámite - Solicitud de Certificado de Legalidad (EX TRA04CUX01)</t>
         </is>
       </c>
       <c r="B373" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C373" s="6" t="n">
-        <v>6.247439158461831e-05</v>
+        <v>6.206871371718574e-05</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>TR02CUX10 Confirmar trámite - Solicitud de Certificado de Legalidad (EX TRA04CUX01)</t>
+          <t>12. TR04CUX12 Certificación de datos</t>
         </is>
       </c>
       <c r="B374" s="5" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C374" s="6" t="n">
-        <v>6.206871371718574e-05</v>
+        <v>6.166303584975315e-05</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>07. MO04CUX07 - Permitido estacionar</t>
+          <t>CU01CUX05 Apertura - Museo Moderno</t>
         </is>
       </c>
       <c r="B375" s="5" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C375" s="6" t="n">
-        <v>6.206871371718574e-05</v>
+        <v>6.125735798232056e-05</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>12. TR04CUX12 Certificación de datos</t>
+          <t>INN10CUX09 Apertura - Experiencia accesibilidad PI</t>
         </is>
       </c>
       <c r="B376" s="5" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C376" s="6" t="n">
-        <v>6.166303584975315e-05</v>
+        <v>6.125735798232056e-05</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>SUA01CUX24 Tipo de login - Residuos fuera del contenedor</t>
+          <t>DEC01CUX01 Apertura - Juventud</t>
         </is>
       </c>
       <c r="B377" s="5" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C377" s="6" t="n">
-        <v>6.125735798232056e-05</v>
+        <v>5.963464651259021e-05</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CU01CUX05 Apertura - Museo Moderno</t>
+          <t>07. MO04CUX07 - Permitido estacionar</t>
         </is>
       </c>
       <c r="B378" s="5" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C378" s="6" t="n">
-        <v>6.125735798232056e-05</v>
+        <v>5.963464651259021e-05</v>
       </c>
     </row>
     <row r="379">
@@ -5375,374 +5375,374 @@
         </is>
       </c>
       <c r="B379" s="5" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C379" s="6" t="n">
-        <v>6.044600224745539e-05</v>
+        <v>5.963464651259021e-05</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>DEC01CUX01 Apertura - Juventud</t>
+          <t>43. TR04CUX43 - Certificado de matrícula</t>
         </is>
       </c>
       <c r="B380" s="5" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C380" s="6" t="n">
-        <v>5.963464651259021e-05</v>
+        <v>5.882329077772504e-05</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CIU05CUX09 Apertura - Caballito</t>
+          <t>Licencias Boti [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B381" s="5" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C381" s="6" t="n">
-        <v>5.922896864515762e-05</v>
+        <v>5.801193504285987e-05</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>43. TR04CUX43 - Certificado de matrícula</t>
+          <t>DH08CUX02  Apertura estático principal - Curso virtual de Educación Financiera</t>
         </is>
       </c>
       <c r="B382" s="5" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C382" s="6" t="n">
-        <v>5.882329077772504e-05</v>
+        <v>5.760625717542728e-05</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>TR04CUX41 Mi argentina - Trámites Nación</t>
+          <t>AM04CUX03 Apertura - Lago Lugano</t>
         </is>
       </c>
       <c r="B383" s="5" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C383" s="6" t="n">
-        <v>5.882329077772504e-05</v>
+        <v>5.760625717542728e-05</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Licencias Boti [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>CU03CUX04 Apertura - Estudio Urbano</t>
         </is>
       </c>
       <c r="B384" s="5" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C384" s="6" t="n">
-        <v>5.801193504285987e-05</v>
+        <v>5.760625717542728e-05</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CU03CUX04 Apertura - Estudio Urbano</t>
+          <t>CU04CUX41 Apertura - Bares Notables</t>
         </is>
       </c>
       <c r="B385" s="5" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C385" s="6" t="n">
-        <v>5.760625717542728e-05</v>
+        <v>5.72005793079947e-05</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>AM04CUX03 Apertura - Lago Lugano</t>
+          <t>18. TR04CUX18 - Clausura de local, obra o ascensor</t>
         </is>
       </c>
       <c r="B386" s="5" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C386" s="6" t="n">
-        <v>5.760625717542728e-05</v>
+        <v>5.679490144056211e-05</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>DH08CUX02  Apertura estático principal - Curso virtual de Educación Financiera</t>
+          <t>01. SA11CUX01 - Dengue</t>
         </is>
       </c>
       <c r="B387" s="5" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C387" s="6" t="n">
-        <v>5.72005793079947e-05</v>
+        <v>5.557786783826435e-05</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CU04CUX41 Apertura - Bares Notables</t>
+          <t>TU03CUX11 Apertura - Floralis Genérica</t>
         </is>
       </c>
       <c r="B388" s="5" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>5.72005793079947e-05</v>
+        <v>5.517218997083176e-05</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>18. TR04CUX18 - Clausura de local, obra o ascensor</t>
+          <t>CU11CUX03 Apertura - Circuito de Espacios Culturales</t>
         </is>
       </c>
       <c r="B389" s="5" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C389" s="6" t="n">
-        <v>5.679490144056211e-05</v>
+        <v>5.436083423596659e-05</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>01. SA11CUX01 - Dengue</t>
+          <t>CU01CUX16 Apertura (post-evento) - Noche de los museos</t>
         </is>
       </c>
       <c r="B390" s="5" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>5.557786783826435e-05</v>
+        <v>5.436083423596659e-05</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>TU03CUX11 Apertura - Floralis Genérica</t>
+          <t>AM04CUX02 Apertura - Jardín Botánico</t>
         </is>
       </c>
       <c r="B391" s="5" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C391" s="6" t="n">
-        <v>5.517218997083176e-05</v>
+        <v>5.3955156368534e-05</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CU11CUX03 Apertura - Circuito de Espacios Culturales</t>
+          <t>TR03CUX06 Apertura - Ministerio de salud - Otros trámites</t>
         </is>
       </c>
       <c r="B392" s="5" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>5.476651210339917e-05</v>
+        <v>5.354947850110142e-05</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CU01CUX16 Apertura (post-evento) - Noche de los museos</t>
+          <t>GA04CUX17 Apertura - Gastronómicos</t>
         </is>
       </c>
       <c r="B393" s="5" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C393" s="6" t="n">
-        <v>5.436083423596659e-05</v>
+        <v>5.314380063366883e-05</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>GA04CUX17 Apertura - Gastronómicos</t>
+          <t>CIU05CUX09 Apertura - Caballito</t>
         </is>
       </c>
       <c r="B394" s="5" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>5.314380063366883e-05</v>
+        <v>5.233244489880366e-05</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>TR03CUX06 Apertura - Ministerio de salud - Otros trámites</t>
+          <t>SE01CUX05 Apertura  - Centro de monitoreo</t>
         </is>
       </c>
       <c r="B395" s="5" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C395" s="6" t="n">
-        <v>5.314380063366883e-05</v>
+        <v>5.233244489880366e-05</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>AM04CUX02 Apertura - Jardín Botánico</t>
+          <t>TR02CUX13 Qué necesito - Solicitud de Partida de defunción</t>
         </is>
       </c>
       <c r="B396" s="5" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>5.273812276623625e-05</v>
+        <v>5.152108916393848e-05</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>TR05CUX04 Apertura - Consulta de deudores morosos</t>
+          <t>SE06CUX01 Apertura - Senderos escolares</t>
         </is>
       </c>
       <c r="B397" s="5" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C397" s="6" t="n">
-        <v>5.233244489880366e-05</v>
+        <v>5.111541129650589e-05</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>SE01CUX05 Apertura  - Centro de monitoreo</t>
+          <t>EDU05CUX05 Apertura - Traductorados</t>
         </is>
       </c>
       <c r="B398" s="5" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>5.233244489880366e-05</v>
+        <v>5.111541129650589e-05</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CIU05CUX01 Autonomía - Casa de Gobierno</t>
+          <t>Test [Test IABA]</t>
         </is>
       </c>
       <c r="B399" s="5" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C399" s="6" t="n">
-        <v>5.192676703137107e-05</v>
+        <v>5.070973342907331e-05</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>EDU05CUX05 Apertura - Traductorados</t>
+          <t>SA07CUX01 Hepatitis B - Salud Sexual y Reproductiva</t>
         </is>
       </c>
       <c r="B400" s="5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>5.111541129650589e-05</v>
+        <v>5.070973342907331e-05</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>SE06CUX01 Apertura - Senderos escolares</t>
+          <t>TR03CUX26 Apertura - Ministerio de Economía y Finanzas</t>
         </is>
       </c>
       <c r="B401" s="5" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C401" s="6" t="n">
-        <v>5.111541129650589e-05</v>
+        <v>5.030405556164072e-05</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>SA07CUX01 Hepatitis B - Salud Sexual y Reproductiva</t>
+          <t>MO04CUX08 Mapa Interactivo - BA Cómo llego</t>
         </is>
       </c>
       <c r="B402" s="5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>5.070973342907331e-05</v>
+        <v>4.989837769420814e-05</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Test [Test IABA]</t>
+          <t>TR05CUX04 Apertura - Consulta de deudores morosos</t>
         </is>
       </c>
       <c r="B403" s="5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C403" s="6" t="n">
-        <v>5.070973342907331e-05</v>
+        <v>4.989837769420814e-05</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>TR03CUX26 Apertura - Ministerio de Economía y Finanzas</t>
+          <t>CIU05CUX01 Autonomía - Casa de Gobierno</t>
         </is>
       </c>
       <c r="B404" s="5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>5.070973342907331e-05</v>
+        <v>4.989837769420814e-05</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MO04CUX08 Mapa Interactivo - BA Cómo llego</t>
+          <t>MO09CUX04 Apertura - Autopista Dellepiane</t>
         </is>
       </c>
       <c r="B405" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C405" s="6" t="n">
-        <v>4.989837769420814e-05</v>
+        <v>4.868134409191038e-05</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>MO09CUX04 Apertura - Autopista Dellepiane</t>
+          <t>TU03CUX01 Apertura fútbol - Estadios de fútbol</t>
         </is>
       </c>
       <c r="B406" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>4.908702195934297e-05</v>
+        <v>4.868134409191038e-05</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>TU03CUX01 Apertura fútbol - Estadios de fútbol</t>
+          <t>DDHH02CUX01 Apertura - Ley Antidiscriminación</t>
         </is>
       </c>
       <c r="B407" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C407" s="6" t="n">
-        <v>4.868134409191038e-05</v>
+        <v>4.827566622447779e-05</v>
       </c>
     </row>
     <row r="408">
@@ -5761,14 +5761,14 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>DDHH02CUX01 Apertura - Ley Antidiscriminación</t>
+          <t>TR04CUX41 Mi argentina - Trámites Nación</t>
         </is>
       </c>
       <c r="B409" s="5" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C409" s="6" t="n">
-        <v>4.827566622447779e-05</v>
+        <v>4.746431048961262e-05</v>
       </c>
     </row>
     <row r="410">
@@ -5787,7 +5787,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Situación de calle [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>AM02CUX01 Apertura - Cambio climático</t>
         </is>
       </c>
       <c r="B411" s="5" t="n">
@@ -5800,7 +5800,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>AM02CUX01 Apertura - Cambio climático</t>
+          <t>Situación de calle [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B412" s="5" t="n">
@@ -5813,14 +5813,14 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TR02CUX13 Qué necesito - Solicitud de Partida de defunción</t>
+          <t>SUA01CUX24 Tipo de login - Residuos fuera del contenedor</t>
         </is>
       </c>
       <c r="B413" s="5" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C413" s="6" t="n">
-        <v>4.462456541758452e-05</v>
+        <v>4.381320968271934e-05</v>
       </c>
     </row>
     <row r="414">
@@ -5852,27 +5852,27 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>EDU04CUX19 Tengo una consulta - Minecraft: Escuelas Reinventando Buenos Aires</t>
+          <t>00. Deporte Adaptado</t>
         </is>
       </c>
       <c r="B416" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C416" s="6" t="n">
-        <v>4.259617608042158e-05</v>
+        <v>4.300185394785416e-05</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>00. Deporte Adaptado</t>
+          <t>TR03CUX07 Apertura Inscripción en el Registro Único de Instituciones Deportivas (RUID) - Subsecretaría de Deportes</t>
         </is>
       </c>
       <c r="B417" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C417" s="6" t="n">
-        <v>4.259617608042158e-05</v>
+        <v>4.300185394785416e-05</v>
       </c>
     </row>
     <row r="418">
@@ -5891,33 +5891,33 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>07. CO08CUX7 - Pista Parque Sarmiento</t>
+          <t>EDU04CUX19 Tengo una consulta - Minecraft: Escuelas Reinventando Buenos Aires</t>
         </is>
       </c>
       <c r="B419" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C419" s="6" t="n">
-        <v>4.137914247812382e-05</v>
+        <v>4.178482034555641e-05</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>TU03CUX09 Apertura - Planetario</t>
+          <t>07. CO08CUX7 - Pista Parque Sarmiento</t>
         </is>
       </c>
       <c r="B420" s="5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C420" s="6" t="n">
-        <v>4.137914247812382e-05</v>
+        <v>4.097346461069124e-05</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura Inscripción en el Registro Único de Instituciones Deportivas (RUID) - Subsecretaría de Deportes</t>
+          <t>CU04CUX60 Apertura - 90 años del Obelisco</t>
         </is>
       </c>
       <c r="B421" s="5" t="n">
@@ -5930,7 +5930,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CU04CUX60 Apertura - 90 años del Obelisco</t>
+          <t>TU03CUX09 Apertura - Planetario</t>
         </is>
       </c>
       <c r="B422" s="5" t="n">
@@ -5982,14 +5982,14 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>03. MO08CUX03 - AUSA - Sacar TelePASE</t>
+          <t>AM04CUX04 Apertura - Paseo Ambiental del Sur</t>
         </is>
       </c>
       <c r="B426" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C426" s="6" t="n">
-        <v>3.975643100839348e-05</v>
+        <v>3.935075314096089e-05</v>
       </c>
     </row>
     <row r="427">
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="B427" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C427" s="6" t="n">
-        <v>3.975643100839348e-05</v>
+        <v>3.935075314096089e-05</v>
       </c>
     </row>
     <row r="428">
@@ -6034,20 +6034,20 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>DH11CUX03 Silencio user - Curso virtual de Identidad de Marca</t>
+          <t>TUR01CUX14 Apertura - Turnera vacunación antigripal</t>
         </is>
       </c>
       <c r="B430" s="5" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C430" s="6" t="n">
-        <v>3.935075314096089e-05</v>
+        <v>3.89450752735283e-05</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>TR01CUX03  Apertura - Solicitud de copia de planos de mensura, horizontalidad, prehorizontalidad y catastro</t>
+          <t>DH11CUX03 Silencio user - Curso virtual de Identidad de Marca</t>
         </is>
       </c>
       <c r="B431" s="5" t="n">
@@ -6060,7 +6060,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>TUR01CUX14 Apertura - Turnera vacunación antigripal</t>
+          <t>AM03CUX04 Apertura Ambiente - Ambiente</t>
         </is>
       </c>
       <c r="B432" s="5" t="n">
@@ -6073,7 +6073,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TR01CUX01 Apertura - GESTIÓN PRIVADA ? CERT. DOCUMENTACIÓN DOCENTES</t>
+          <t>TR01CUX01 Apertura - GESTIÓN PRIVADA – CERT. DOCUMENTACIÓN DOCENTES</t>
         </is>
       </c>
       <c r="B433" s="5" t="n">
@@ -6099,53 +6099,53 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>AM04CUX04 Apertura - Paseo Ambiental del Sur</t>
+          <t>TR01CUX03  Apertura - Solicitud de copia de planos de mensura, horizontalidad, prehorizontalidad y catastro</t>
         </is>
       </c>
       <c r="B435" s="5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C435" s="6" t="n">
-        <v>3.853939740609571e-05</v>
+        <v>3.813371953866313e-05</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>AM03CUX04 Apertura Ambiente - Ambiente</t>
+          <t>TU01CUX05 Apertura - Seguridad turística</t>
         </is>
       </c>
       <c r="B436" s="5" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C436" s="6" t="n">
-        <v>3.813371953866313e-05</v>
+        <v>3.732236380379796e-05</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>TU01CUX05 Apertura - Seguridad turística</t>
+          <t>DDHH03CUX09 Apertura - Programa Abrazar</t>
         </is>
       </c>
       <c r="B437" s="5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C437" s="6" t="n">
-        <v>3.772804167123054e-05</v>
+        <v>3.691668593636537e-05</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>DDHH03CUX09 Apertura - Programa Abrazar</t>
+          <t>SE01CUX04 Apertura - Bomberos</t>
         </is>
       </c>
       <c r="B438" s="5" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C438" s="6" t="n">
-        <v>3.732236380379796e-05</v>
+        <v>3.651100806893279e-05</v>
       </c>
     </row>
     <row r="439">
@@ -6155,192 +6155,192 @@
         </is>
       </c>
       <c r="B439" s="5" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C439" s="6" t="n">
-        <v>3.691668593636537e-05</v>
+        <v>3.61053302015002e-05</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>SE01CUX04 Apertura - Bomberos</t>
+          <t>SA16CUX02 Apertura - Sarampión</t>
         </is>
       </c>
       <c r="B440" s="5" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C440" s="6" t="n">
-        <v>3.691668593636537e-05</v>
+        <v>3.61053302015002e-05</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SA16CUX02 Apertura - Sarampión</t>
+          <t>MO06CUX03 Apertura - Pedaleá con Boti</t>
         </is>
       </c>
       <c r="B441" s="5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C441" s="6" t="n">
-        <v>3.651100806893279e-05</v>
+        <v>3.569965233406761e-05</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MO06CUX03 Apertura - Pedaleá con Boti</t>
+          <t>TU03CUX10 Apertura - Colección Fortabat</t>
         </is>
       </c>
       <c r="B442" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C442" s="6" t="n">
-        <v>3.569965233406761e-05</v>
+        <v>3.529397446663502e-05</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TR01CUX09 Apertura - Certificado de Información Catastral</t>
+          <t>SUACI - Autos abandonados</t>
         </is>
       </c>
       <c r="B443" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C443" s="6" t="n">
-        <v>3.569965233406761e-05</v>
+        <v>3.529397446663502e-05</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>TU03CUX10 Apertura - Colección Fortabat</t>
+          <t>TR01CUX09 Apertura - Certificado de Información Catastral</t>
         </is>
       </c>
       <c r="B444" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C444" s="6" t="n">
-        <v>3.529397446663502e-05</v>
+        <v>3.488829659920244e-05</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>SUACI - Autos abandonados</t>
+          <t>DH05CUX01 Adicción al juego - Adicciones</t>
         </is>
       </c>
       <c r="B445" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C445" s="6" t="n">
-        <v>3.529397446663502e-05</v>
+        <v>3.488829659920244e-05</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>DH05CUX01 Adicción al juego - Adicciones</t>
+          <t>CU08CUX01  Apertura de contingencia II - Vacaciones de invierno 2025</t>
         </is>
       </c>
       <c r="B446" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C446" s="6" t="n">
-        <v>3.488829659920244e-05</v>
+        <v>3.448261873176985e-05</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>EM03CUX02 Apertura - Academia BA Emprende</t>
+          <t>05. Parque de la Ciudad</t>
         </is>
       </c>
       <c r="B447" s="5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C447" s="6" t="n">
-        <v>3.448261873176985e-05</v>
+        <v>3.367126299690468e-05</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CU08CUX01  Apertura de contingencia II - Vacaciones de invierno 2025</t>
+          <t>NI01CUX05 Boticuentos  - Boticuentos 2023: Superapertura y CC</t>
         </is>
       </c>
       <c r="B448" s="5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C448" s="6" t="n">
-        <v>3.448261873176985e-05</v>
+        <v>3.367126299690468e-05</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>04. TR04CUX04 - Registro de artistas callejeros</t>
+          <t>EM03CUX02 Apertura - Academia BA Emprende</t>
         </is>
       </c>
       <c r="B449" s="5" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C449" s="6" t="n">
-        <v>3.407694086433726e-05</v>
+        <v>3.285990726203951e-05</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>NI01CUX05 Boticuentos  - Boticuentos 2023: Superapertura y CC</t>
+          <t>Derivación a agente de AGC</t>
         </is>
       </c>
       <c r="B450" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C450" s="6" t="n">
-        <v>3.326558512947209e-05</v>
+        <v>3.285990726203951e-05</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
+          <t>TR01CUX18  Apertura - Solicitud de antecedentes de habilitaciones</t>
         </is>
       </c>
       <c r="B451" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C451" s="6" t="n">
-        <v>3.285990726203951e-05</v>
+        <v>3.245422939460692e-05</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Derivación a agente de AGC</t>
+          <t>01. DEC03CUXO1 - Patrocinio BA</t>
         </is>
       </c>
       <c r="B452" s="5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C452" s="6" t="n">
-        <v>3.285990726203951e-05</v>
+        <v>3.204855152717433e-05</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>05. Parque de la Ciudad</t>
+          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
         </is>
       </c>
       <c r="B453" s="5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C453" s="6" t="n">
-        <v>3.285990726203951e-05</v>
+        <v>3.204855152717433e-05</v>
       </c>
     </row>
     <row r="454">
@@ -6359,7 +6359,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TR01CUX18  Apertura - Solicitud de antecedentes de habilitaciones</t>
+          <t>04. TR04CUX04 - Registro de artistas callejeros</t>
         </is>
       </c>
       <c r="B455" s="5" t="n">
@@ -6385,20 +6385,20 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>01. DEC03CUXO1 - Patrocinio BA</t>
+          <t>20. TR04CUX20 - Dirección General de Mesa de Entradas, Salidas y Archivo</t>
         </is>
       </c>
       <c r="B457" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C457" s="6" t="n">
-        <v>3.083151792487657e-05</v>
+        <v>3.00201621900114e-05</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Apertura - Adopción GCBA</t>
+          <t>TR01CUX15 Apertura - TAD Registro de Empleadores</t>
         </is>
       </c>
       <c r="B458" s="5" t="n">
@@ -6411,59 +6411,59 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>20. TR04CUX20 - Dirección General de Mesa de Entradas, Salidas y Archivo</t>
+          <t>DDHH03CUX02 Apertura - Adopción GCBA</t>
         </is>
       </c>
       <c r="B459" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C459" s="6" t="n">
-        <v>2.920880645514623e-05</v>
+        <v>2.880312858771364e-05</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TR01CUX15 Apertura - TAD Registro de Empleadores</t>
+          <t>CIU05CUX03 Montserrat - Palermo</t>
         </is>
       </c>
       <c r="B460" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C460" s="6" t="n">
-        <v>2.880312858771364e-05</v>
+        <v>2.839745072028105e-05</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CIU05CUX03 Montserrat - Belgrano</t>
+          <t>TR03CUX17 Trámites vehículos - Desarrollo urbano y transporte - Transporte</t>
         </is>
       </c>
       <c r="B461" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C461" s="6" t="n">
-        <v>2.839745072028105e-05</v>
+        <v>2.799177285284847e-05</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>TR03CUX17 Trámites vehículos - Desarrollo urbano y transporte - Transporte</t>
+          <t>OB05CUX01 Número de expediente - Consulta DGROC</t>
         </is>
       </c>
       <c r="B462" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C462" s="6" t="n">
-        <v>2.799177285284847e-05</v>
+        <v>2.71804171179833e-05</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>OB05CUX01 Número de expediente - Consulta DGROC</t>
+          <t>Coronavirus 2022 [Derivación a Boti]</t>
         </is>
       </c>
       <c r="B463" s="5" t="n">
@@ -6476,7 +6476,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Derivación a Boti [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>EDU04CUX28 Apertura - Cambio de escuela</t>
         </is>
       </c>
       <c r="B464" s="5" t="n">
@@ -6489,20 +6489,20 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>EDU04CUX28 Apertura - Cambio de escuela</t>
+          <t>SUA01CUX27 Pedido de dirección - Mayor luminaria</t>
         </is>
       </c>
       <c r="B465" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C465" s="6" t="n">
-        <v>2.71804171179833e-05</v>
+        <v>2.677473925055071e-05</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>EDU04CUX01 CEC - CEC</t>
+          <t>02. Clubes de Barrio DE03CUX02</t>
         </is>
       </c>
       <c r="B466" s="5" t="n">
@@ -6515,7 +6515,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>02. Clubes de Barrio DE03CUX02</t>
+          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
         </is>
       </c>
       <c r="B467" s="5" t="n">
@@ -6528,7 +6528,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
+          <t>EDU04CUX01 CEC - CEC</t>
         </is>
       </c>
       <c r="B468" s="5" t="n">
@@ -6567,46 +6567,46 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>TR03CUX08 Seguridad alimentaria - AGC</t>
+          <t>Identificación Tardía</t>
         </is>
       </c>
       <c r="B471" s="5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C471" s="6" t="n">
-        <v>2.515202778082036e-05</v>
+        <v>2.474634991338777e-05</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Identificación Tardía</t>
+          <t>SUA01CUX34 Lavado de contenedor - Vaciado de contenedor</t>
         </is>
       </c>
       <c r="B472" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C472" s="6" t="n">
-        <v>2.474634991338777e-05</v>
+        <v>2.434067204595519e-05</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>SUA01CUX27 Pedido de dirección - Mayor luminaria</t>
+          <t>El usuario ha enviado una ubicación [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B473" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C473" s="6" t="n">
-        <v>2.474634991338777e-05</v>
+        <v>2.434067204595519e-05</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>SUA01CUX34 Lavado de contenedor - Vaciado de contenedor</t>
+          <t>CO08CUX06 Apertura - Skatepark Villa Luro</t>
         </is>
       </c>
       <c r="B474" s="5" t="n">
@@ -6619,27 +6619,27 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CO08CUX06 Apertura - Skatepark Villa Luro</t>
+          <t>JU02CUX01 Apertura - Consejo de la Magistratura</t>
         </is>
       </c>
       <c r="B475" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C475" s="6" t="n">
-        <v>2.434067204595519e-05</v>
+        <v>2.39349941785226e-05</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>El usuario ha enviado una ubicación [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>03. AM03CUX03 - Red de Refugios Climáticos</t>
         </is>
       </c>
       <c r="B476" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C476" s="6" t="n">
-        <v>2.434067204595519e-05</v>
+        <v>2.352931631109002e-05</v>
       </c>
     </row>
     <row r="477">
@@ -6658,7 +6658,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>00. REVISAR ?? [limpiar variables]</t>
+          <t>00. REVISAR ⚠️ [limpiar variables]</t>
         </is>
       </c>
       <c r="B478" s="5" t="n">
@@ -6671,20 +6671,20 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>JU02CUX01 Apertura - Consejo de la Magistratura</t>
+          <t>MO10CUX01 Apertura - Superapertura Metrobus</t>
         </is>
       </c>
       <c r="B479" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C479" s="6" t="n">
-        <v>2.352931631109002e-05</v>
+        <v>2.312363844365743e-05</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>03. AM03CUX03 - Red de Refugios Climáticos</t>
+          <t>DH07CUX01 Apertura - Redes por la Inclusión</t>
         </is>
       </c>
       <c r="B480" s="5" t="n">
@@ -6723,79 +6723,79 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
+          <t>TR03CUX17 Certificado de recupero del vehículo fuera de término - Desarrollo urbano y transporte - Transporte</t>
         </is>
       </c>
       <c r="B483" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C483" s="6" t="n">
-        <v>2.271796057622484e-05</v>
+        <v>2.231228270879226e-05</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>TR03CUX17 Certificado de recupero del vehículo fuera de término - Desarrollo urbano y transporte - Transporte</t>
+          <t>TR03CUX08 Seguridad alimentaria - AGC</t>
         </is>
       </c>
       <c r="B484" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C484" s="6" t="n">
-        <v>2.231228270879226e-05</v>
+        <v>2.150092697392708e-05</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>MO10CUX01 Apertura - Superapertura Metrobus</t>
+          <t>DE05CUX02 Qué actividades hay - Deportes en barrios</t>
         </is>
       </c>
       <c r="B485" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C485" s="6" t="n">
-        <v>2.150092697392708e-05</v>
+        <v>2.10952491064945e-05</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>DH07CUX01 Apertura - Redes por la Inclusión</t>
+          <t>TR04CUX01 Apertura - Certificado de aptitud ambiental</t>
         </is>
       </c>
       <c r="B486" s="5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C486" s="6" t="n">
-        <v>2.150092697392708e-05</v>
+        <v>2.028389337162932e-05</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>DE05CUX02 Qué actividades hay - Deportes en barrios</t>
+          <t>DDHH03CUX05 Apertura - Observatorio SIPROID</t>
         </is>
       </c>
       <c r="B487" s="5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C487" s="6" t="n">
-        <v>2.068957123906191e-05</v>
+        <v>1.987821550419674e-05</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>TR04CUX01 Apertura - Certificado de aptitud ambiental</t>
+          <t>SA16CUX02 Quiero vacunarme - Sarampión</t>
         </is>
       </c>
       <c r="B488" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C488" s="6" t="n">
-        <v>2.028389337162932e-05</v>
+        <v>1.947253763676415e-05</v>
       </c>
     </row>
     <row r="489">
@@ -6814,20 +6814,20 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>DDHH03CUX05 Apertura - Observatorio SIPROID</t>
+          <t>AM04CUX06 Apertura - Reserva Ecológica Ciudad Universitaria Costanera Norte</t>
         </is>
       </c>
       <c r="B490" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C490" s="6" t="n">
-        <v>1.947253763676415e-05</v>
+        <v>1.906685976933157e-05</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>TR03CUX17 Tarjeta control - Desarrollo urbano y transporte - Transporte</t>
+          <t>TR02CUX12 Qué necesito - Solicitud Partida de Matrimonio</t>
         </is>
       </c>
       <c r="B491" s="5" t="n">
@@ -6840,7 +6840,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>TR02CUX12 Qué necesito - Solicitud Partida de Matrimonio</t>
+          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
         </is>
       </c>
       <c r="B492" s="5" t="n">
@@ -6853,7 +6853,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>05. CIU05CUX05 Buscar Código Postal</t>
+          <t>TR03CUX17 Tarjeta control - Desarrollo urbano y transporte - Transporte</t>
         </is>
       </c>
       <c r="B493" s="5" t="n">
@@ -6879,7 +6879,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>AM04CUX06 Apertura - Reserva Ecológica Ciudad Universitaria Costanera Norte</t>
+          <t>05. CIU05CUX05 Buscar Código Postal</t>
         </is>
       </c>
       <c r="B495" s="5" t="n">
@@ -6892,59 +6892,59 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>SA16CUX02 Quiero vacunarme - Sarampión</t>
+          <t>GE03CUX03 Apertura - Personas que cuidan</t>
         </is>
       </c>
       <c r="B496" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C496" s="6" t="n">
-        <v>1.866118190189898e-05</v>
+        <v>1.78498261670338e-05</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>INN01CUX01 Apertura de contingencia - Superapertura BA Gaming</t>
+          <t>26. TR04CUX26 - Disolución de Unión Civil | Convivencial</t>
         </is>
       </c>
       <c r="B497" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C497" s="6" t="n">
-        <v>1.825550403446639e-05</v>
+        <v>1.78498261670338e-05</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>AM03CUX05 Superapertura - Superapertura Sustentabilidad</t>
+          <t>SA08CUX01 Apertura - Donación de sangre 🩸</t>
         </is>
       </c>
       <c r="B498" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C498" s="6" t="n">
-        <v>1.825550403446639e-05</v>
+        <v>1.78498261670338e-05</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>TR03CUX27  Apertura - Ministerio de Justicia y Seguridad</t>
+          <t>AM03CUX05 Superapertura - Superapertura Sustentabilidad</t>
         </is>
       </c>
       <c r="B499" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C499" s="6" t="n">
-        <v>1.825550403446639e-05</v>
+        <v>1.78498261670338e-05</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>26. TR04CUX26 - Disolución de Unión Civil | Convivencial</t>
+          <t>DH05CUX01 Apertura  - Adicciones</t>
         </is>
       </c>
       <c r="B500" s="5" t="n">
@@ -6957,7 +6957,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>DH05CUX01 Apertura  - Adicciones</t>
+          <t>TR03CUX27  Apertura - Ministerio de Justicia y Seguridad</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
@@ -6970,20 +6970,20 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>GE03CUX03 Apertura - Personas que cuidan</t>
+          <t>Inspecciones Programadas - Problemas</t>
         </is>
       </c>
       <c r="B502" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C502" s="6" t="n">
-        <v>1.78498261670338e-05</v>
+        <v>1.744414829960122e-05</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>TR04CUX41 Clave Fiscal - Trámites Nación</t>
+          <t>INN01CUX01 Apertura de contingencia - Superapertura BA Gaming</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -6996,7 +6996,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>MO06CUX01 Dónde dejar la bici - Ciclovías</t>
+          <t>DH11CUX02 Chat por whatsapp - Identidad de marca (estático)</t>
         </is>
       </c>
       <c r="B504" s="5" t="n">
@@ -7009,7 +7009,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Inspecciones Programadas - Problemas</t>
+          <t>TR04CUX41 Clave Fiscal - Trámites Nación</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -7022,7 +7022,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>DH11CUX02 Chat por whatsapp - Identidad de marca (estático)</t>
+          <t>DH02CUX01 Apertura - RUPEPYS</t>
         </is>
       </c>
       <c r="B506" s="5" t="n">
@@ -7035,7 +7035,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>SA08CUX01 Apertura - Donación de sangre ??</t>
+          <t>EDU04CUX32 Apertura  - Violencia en escuelas</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
@@ -7048,7 +7048,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>EDU04CUX32 Apertura  - Violencia en escuelas</t>
+          <t>CU01CUX15 Apertura Experiencia Interactiva - MIJU experiencia interactiva</t>
         </is>
       </c>
       <c r="B508" s="5" t="n">
@@ -7061,92 +7061,92 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CU01CUX15 Apertura Experiencia Interactiva - MIJU experiencia interactiva</t>
+          <t>MO06CUX01 Dónde dejar la bici - Bicicletas</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C509" s="6" t="n">
-        <v>1.703847043216863e-05</v>
+        <v>1.663279256473605e-05</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>05. EDU03CUX05 - Universidad de la Ciudad</t>
+          <t>VI01CUX05 Apertura - Programa Ley 624</t>
         </is>
       </c>
       <c r="B510" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C510" s="6" t="n">
-        <v>1.663279256473605e-05</v>
+        <v>1.622711469730346e-05</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>DH02CUX01 Apertura - RUPEPYS</t>
+          <t>05. EDU03CUX05 - Universidad de la Ciudad</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C511" s="6" t="n">
-        <v>1.622711469730346e-05</v>
+        <v>1.582143682987087e-05</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>TR03CUX03 Proteatro - Cultura</t>
+          <t>CU01CUX02 Apertura - Museos</t>
         </is>
       </c>
       <c r="B512" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C512" s="6" t="n">
-        <v>1.622711469730346e-05</v>
+        <v>1.582143682987087e-05</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>TR03CUX05 Biblioteca Docente - Ministerio de Educación e Innovación - Otros trámites</t>
+          <t>06. CIU05CUX06 Búsqueda de farmacias</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C513" s="6" t="n">
-        <v>1.582143682987087e-05</v>
+        <v>1.50100810950057e-05</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>EDU04CUX26 Número no encontrado - Preinscripción escolar</t>
+          <t>TR03CUX05 Biblioteca Docente - Ministerio de Educación e Innovación - Otros trámites</t>
         </is>
       </c>
       <c r="B514" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C514" s="6" t="n">
-        <v>1.582143682987087e-05</v>
+        <v>1.50100810950057e-05</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>JU03CUX01 Apertura - Patrocinio penal</t>
+          <t>CU04CUX55 Apertura - Festival Ciudad Joven BA</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C515" s="6" t="n">
-        <v>1.541575896243829e-05</v>
+        <v>1.50100810950057e-05</v>
       </c>
     </row>
     <row r="516">
@@ -7156,49 +7156,49 @@
         </is>
       </c>
       <c r="B516" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C516" s="6" t="n">
-        <v>1.541575896243829e-05</v>
+        <v>1.50100810950057e-05</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>CU04CUX55 Apertura - Festival Ciudad Joven BA</t>
+          <t>MO06CUX01 Apertura - Bicicletas</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C517" s="6" t="n">
-        <v>1.50100810950057e-05</v>
+        <v>1.460440322757311e-05</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>06. CIU05CUX06 Búsqueda de farmacias</t>
+          <t>JU03CUX01 Apertura - Patrocinio penal</t>
         </is>
       </c>
       <c r="B518" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C518" s="6" t="n">
-        <v>1.50100810950057e-05</v>
+        <v>1.460440322757311e-05</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>VI01CUX05 Apertura - Programa Ley 624</t>
+          <t>TR01CUX20 Apertura - Subsanación de Faltas Documentales</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C519" s="6" t="n">
-        <v>1.460440322757311e-05</v>
+        <v>1.419872536014053e-05</v>
       </c>
     </row>
     <row r="520">
@@ -7230,14 +7230,14 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>MO06CUX01 Apertura - Ciclovías</t>
+          <t>TR04CUX16 Apertura - Certificado Negativo de Inscripción de Nacimiento</t>
         </is>
       </c>
       <c r="B522" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C522" s="6" t="n">
-        <v>1.338736962527535e-05</v>
+        <v>1.379304749270794e-05</v>
       </c>
     </row>
     <row r="523">
@@ -7256,14 +7256,14 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>TR04CUX16 Apertura - Certificado Negativo de Inscripción de Nacimiento</t>
+          <t>TR03CUX28 CUIT - Nación</t>
         </is>
       </c>
       <c r="B524" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C524" s="6" t="n">
-        <v>1.338736962527535e-05</v>
+        <v>1.298169175784277e-05</v>
       </c>
     </row>
     <row r="525">
@@ -7295,20 +7295,20 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>SUA01CUX27 Dónde ubicar la luminaria - Mayor luminaria</t>
+          <t>05. CIU05CUX05 Buscar Código Postal</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C527" s="6" t="n">
-        <v>1.298169175784277e-05</v>
+        <v>1.257601389041018e-05</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>TR01CUX20 Apertura - Subsanación de Faltas Documentales</t>
+          <t>TR03CUX03 Proteatro - Cultura</t>
         </is>
       </c>
       <c r="B528" s="5" t="n">
@@ -7334,20 +7334,20 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>05. RC01CUX05 - Certificación de firmas</t>
+          <t>02. GE01CUX02 - Violencia contra la mujer</t>
         </is>
       </c>
       <c r="B530" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C530" s="6" t="n">
-        <v>1.217033602297759e-05</v>
+        <v>1.176465815554501e-05</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>DH11CUX04 Apertura - Curso Fotoproducto (estático)</t>
+          <t>EDU04CUX26 Número no encontrado - Preinscripción escolar</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
@@ -7360,7 +7360,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>02. GE01CUX02 - Violencia contra la mujer</t>
+          <t>CU10CUX02 Clemente - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
@@ -7373,7 +7373,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>05. CIU05CUX05 Buscar Código Postal</t>
+          <t>TR03CUX25 Terminales de pago - Ministerio de Desarrollo Urbano y Transporte - DGROC CATASTRO</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -7386,20 +7386,20 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CU10CUX02 La Jirafa - Paseo de la historieta</t>
+          <t>05. RC01CUX05 - Certificación de firmas</t>
         </is>
       </c>
       <c r="B534" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C534" s="6" t="n">
-        <v>1.095330242067983e-05</v>
+        <v>1.135898028811242e-05</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>z. Personas mayores - Viejos</t>
+          <t>CU10CUX02 La Jirafa - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
@@ -7412,7 +7412,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>CU01CUX02 Apertura - Museos</t>
+          <t>z. Personas mayores - Viejos</t>
         </is>
       </c>
       <c r="B536" s="5" t="n">
@@ -7425,20 +7425,20 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>TR03CUX25 Terminales de pago - Ministerio de Desarrollo Urbano y Transporte - DGROC CATASTRO</t>
+          <t>AC02CUX03 Emergencias 911 - Emergencias PFA</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C537" s="6" t="n">
-        <v>1.095330242067983e-05</v>
+        <v>1.054762455324725e-05</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>AC02CUX03 Emergencias 911 - Emergencias PFA</t>
+          <t>INN10CUX15 Límite de consultas - Agente Donde Estacionar</t>
         </is>
       </c>
       <c r="B538" s="5" t="n">
@@ -7451,7 +7451,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>INN10CUX15 Límite de consultas - Agente Donde Estacionar</t>
+          <t>05. EDU03CUX05 - Universidad de la Ciudad</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
@@ -7464,20 +7464,20 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>CU10CUX02 Clemente - Paseo de la historieta</t>
+          <t>EDU04CUX30 Adolescencia  - Uso del celular</t>
         </is>
       </c>
       <c r="B540" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C540" s="6" t="n">
-        <v>1.014194668581466e-05</v>
+        <v>1.054762455324725e-05</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>05. CIU05CUX05 Buscar Código Postal</t>
+          <t>SUA01CUX27 Dónde ubicar la luminaria - Mayor luminaria</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
@@ -7490,7 +7490,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>15. TU03CUX11 - Floralis Genérica</t>
+          <t>05. CIU05CUX05 Buscar Código Postal</t>
         </is>
       </c>
       <c r="B542" s="5" t="n">
@@ -7516,7 +7516,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>05. EDU03CUX05 - Universidad de la Ciudad</t>
+          <t>15. TU03CUX11 - Floralis Genérica</t>
         </is>
       </c>
       <c r="B544" s="5" t="n">
@@ -7529,20 +7529,20 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>AC02CUX04 SAME - Emergencias</t>
+          <t>INN01CUX01 Apertura - Superapertura BA Gaming</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C545" s="6" t="n">
-        <v>9.736268818382076e-06</v>
+        <v>1.014194668581466e-05</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>TR02CUX07 Apertura - BAID Ya se usó para ese trámite - Estado abierto</t>
+          <t>DH11CUX04 Apertura - Curso Fotoproducto (estático)</t>
         </is>
       </c>
       <c r="B546" s="5" t="n">
@@ -7555,124 +7555,124 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>fulfilled of Condición [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>TR02CUX07 Apertura - BAID Ya se usó para ese trámite - Estado abierto</t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C547" s="6" t="n">
-        <v>9.33059095094949e-06</v>
+        <v>9.736268818382076e-06</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>DDHH03CUX01 Superapertura - Bifurcador Derechos de Niños_as y Adolescentes</t>
+          <t>AC02CUX04 SAME - Emergencias</t>
         </is>
       </c>
       <c r="B548" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C548" s="6" t="n">
-        <v>9.33059095094949e-06</v>
+        <v>9.736268818382076e-06</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>CU08CUX02 Apertura post evento - Verano BA 2024</t>
+          <t>DDHH03CUX01 Superapertura - Bifurcador Derechos de Niños_as y Adolescentes</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C549" s="6" t="n">
-        <v>9.33059095094949e-06</v>
+        <v>9.736268818382076e-06</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>TR03CUX26 Apertura | Cajas Habilitadas  - Ministerio de Economía y Finanzas</t>
+          <t>fulfilled of Condición [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B550" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C550" s="6" t="n">
-        <v>8.924913083516902e-06</v>
+        <v>9.33059095094949e-06</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>TU03CUX06 Apertura - Casa Rosada</t>
+          <t>TR05CUX04 No figura en el registro - Consulta de deudores morosos</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C551" s="6" t="n">
-        <v>8.924913083516902e-06</v>
+        <v>9.33059095094949e-06</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>DE05CUX04 Apertura - Autódromo</t>
+          <t>CU08CUX02 Apertura post evento - Verano BA 2024</t>
         </is>
       </c>
       <c r="B552" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C552" s="6" t="n">
-        <v>8.924913083516902e-06</v>
+        <v>9.33059095094949e-06</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>TR03CUX08 Habilitaciones - AGC</t>
+          <t>TR03CUX26 Apertura | Cajas Habilitadas  - Ministerio de Economía y Finanzas</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C553" s="6" t="n">
-        <v>8.924913083516902e-06</v>
+        <v>9.33059095094949e-06</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SUACI Componentes Comunes</t>
+          <t>TR03CUX08 Habilitaciones - AGC</t>
         </is>
       </c>
       <c r="B554" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C554" s="6" t="n">
-        <v>8.519235216084316e-06</v>
+        <v>8.924913083516902e-06</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>INN01CUX01 Apertura - Superapertura BA Gaming</t>
+          <t>TU03CUX06 Apertura - Casa Rosada</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C555" s="6" t="n">
-        <v>8.519235216084316e-06</v>
+        <v>8.924913083516902e-06</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>26. TR04CUX26 - Disolución de Unión Civil | Convivencial</t>
+          <t>CU10CUX02 Paseo de Historietas - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B556" s="5" t="n">
@@ -7698,176 +7698,176 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>EDU04CUX23 Apertura - Escuela de verano</t>
+          <t>DE05CUX04 Apertura - Autódromo</t>
         </is>
       </c>
       <c r="B558" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C558" s="6" t="n">
-        <v>8.11355734865173e-06</v>
+        <v>8.519235216084316e-06</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>MO06CUX02 Cómo usar Ecobici - Ecobici</t>
+          <t>26. TR04CUX26 - Disolución de Unión Civil | Convivencial</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C559" s="6" t="n">
-        <v>7.707879481219143e-06</v>
+        <v>8.519235216084316e-06</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Adolescencia  - Uso del celular</t>
+          <t>SUACI Componentes Comunes</t>
         </is>
       </c>
       <c r="B560" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C560" s="6" t="n">
-        <v>7.707879481219143e-06</v>
+        <v>8.519235216084316e-06</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>14. SUA01CUX14 - Reparación de Baches</t>
+          <t>Identificación Tardía</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C561" s="6" t="n">
-        <v>7.707879481219143e-06</v>
+        <v>8.11355734865173e-06</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>CU10CUX02 Paseo de Historietas - Paseo de la historieta</t>
+          <t>EDU04CUX23 Apertura - Escuela de verano</t>
         </is>
       </c>
       <c r="B562" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C562" s="6" t="n">
-        <v>7.707879481219143e-06</v>
+        <v>8.11355734865173e-06</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>02. Comunas de la ciudad</t>
+          <t>Identificación Tardía</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C563" s="6" t="n">
-        <v>7.707879481219143e-06</v>
+        <v>8.11355734865173e-06</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>NI02CUX01 Tiempo libre - SAP de Niñez y Adolescencia</t>
+          <t>02. Comunas de la ciudad</t>
         </is>
       </c>
       <c r="B564" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C564" s="6" t="n">
-        <v>7.302201613786556e-06</v>
+        <v>7.707879481219143e-06</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Rendir subsidio 690 [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>MO06CUX02 Cómo usar Ecobici - Ecobici</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C565" s="6" t="n">
-        <v>7.302201613786556e-06</v>
+        <v>7.707879481219143e-06</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>0. Core del bot (No tocar) [Inactividad  del usuario: limpiar datos de sesión]</t>
+          <t>CIU05CUX01 Apertura - Casa de Gobierno</t>
         </is>
       </c>
       <c r="B566" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C566" s="6" t="n">
-        <v>7.302201613786556e-06</v>
+        <v>7.707879481219143e-06</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Identificación Tardía</t>
+          <t>14. SUA01CUX14 - Reparación de Baches</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C567" s="6" t="n">
-        <v>6.89652374635397e-06</v>
+        <v>7.707879481219143e-06</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>SA08CUX02 Apertura - Donación de órganos ??</t>
+          <t>0. Core del bot (No tocar) [Inactividad  del usuario: limpiar datos de sesión]</t>
         </is>
       </c>
       <c r="B568" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C568" s="6" t="n">
-        <v>6.89652374635397e-06</v>
+        <v>7.302201613786556e-06</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Z. Apagados, detonables ?? [SA01CUX07 - Formulario para declarar vacuna]</t>
+          <t>Rendir subsidio 690 [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C569" s="6" t="n">
-        <v>6.89652374635397e-06</v>
+        <v>7.302201613786556e-06</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>SA07CUX01 VIH - Salud Sexual y Reproductiva</t>
+          <t>NI02CUX01 Tiempo libre - SAP de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="B570" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C570" s="6" t="n">
-        <v>6.89652374635397e-06</v>
+        <v>7.302201613786556e-06</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>TR05CUX04 No figura en el registro - Consulta de deudores morosos</t>
+          <t>Z. Apagados, detonables 💣 [SA01CUX07 - Formulario para declarar vacuna]</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -7880,7 +7880,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>00. REVISAR ?? [Desambiguador deudas]</t>
+          <t>SA07CUX01 VIH - Salud Sexual y Reproductiva</t>
         </is>
       </c>
       <c r="B572" s="5" t="n">
@@ -7893,7 +7893,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
+          <t>00. REVISAR ⚠️ [Desambiguador deudas]</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -7906,7 +7906,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CIU04CUX01 Recomendaciones - Estadisticas y Censos</t>
+          <t>SA08CUX02 Apertura - Donación de órganos ❤️</t>
         </is>
       </c>
       <c r="B574" s="5" t="n">
@@ -7919,85 +7919,85 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>EP04CUX01 Apertura sin registro contingencia - Ecopuntos</t>
+          <t>MO05CUX12 Cómo es el trámite - Ampliación de licencias interjurisdiccional</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C575" s="6" t="n">
-        <v>6.085168011488797e-06</v>
+        <v>6.490845878921383e-06</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Identificación Tardía</t>
+          <t>CIU04CUX01 Recomendaciones - Estadisticas y Censos</t>
         </is>
       </c>
       <c r="B576" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C576" s="6" t="n">
-        <v>6.085168011488797e-06</v>
+        <v>6.490845878921383e-06</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CIU05CUX01 Apertura - Casa de Gobierno</t>
+          <t>05. RC01CUX05 - Certificación de firmas</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C577" s="6" t="n">
-        <v>5.679490144056211e-06</v>
+        <v>6.490845878921383e-06</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>EDU04CUX02 Apertura - Buscador de distritos</t>
+          <t>EP04CUX01 Apertura sin registro contingencia - Ecopuntos</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C578" s="6" t="n">
-        <v>5.679490144056211e-06</v>
+        <v>6.085168011488797e-06</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>05. CIU05CUX05 Buscar Código Postal</t>
+          <t>VI03CUX01  Quién puede pedirlo - Créditos Hipotecarios</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C579" s="6" t="n">
-        <v>5.679490144056211e-06</v>
+        <v>6.085168011488797e-06</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>AM03CUX04 Áreas Protegidas - Ambiente</t>
+          <t>17. EDU04CUX17 - App miEscuela</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C580" s="6" t="n">
-        <v>5.679490144056211e-06</v>
+        <v>6.085168011488797e-06</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>TR03CUX16 Denuncia a administradores de consorcio - Defensa del consumidor</t>
+          <t>EDU04CUX02 Apertura - Buscador de distritos</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -8023,59 +8023,59 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>17. EDU04CUX17 - App miEscuela</t>
+          <t>DH11CUX08 Video 1 - Compras con impacto</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C583" s="6" t="n">
-        <v>5.273812276623624e-06</v>
+        <v>5.679490144056211e-06</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>CU04CUX16 Apertura contingencia - BA Inspira</t>
+          <t>05. CIU05CUX05 Buscar Código Postal</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C584" s="6" t="n">
-        <v>5.273812276623624e-06</v>
+        <v>5.679490144056211e-06</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>DH11CUX08 Introducción - Compras con impacto</t>
+          <t>CU04CUX16 Apertura contingencia - BA Inspira</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C585" s="6" t="n">
-        <v>4.868134409191038e-06</v>
+        <v>5.273812276623624e-06</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>0. Core del bot (No tocar) [Tagear IA Off]</t>
+          <t>AM03CUX04 Áreas Protegidas - Ambiente</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C586" s="6" t="n">
-        <v>4.868134409191038e-06</v>
+        <v>5.273812276623624e-06</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>04. SA02CUX04 - Hisopado COVID-19 - Consulta y resultado</t>
+          <t>CU08CUX07 Apertura de contingencia  - Carnavales 2026</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -8088,7 +8088,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>05. RC01CUX05 - Certificación de firmas</t>
+          <t>02. DH11CUX02 Identidad de marca (estático)</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
@@ -8101,7 +8101,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CU08CUX07 Apertura de contingencia  - Carnavales 2026</t>
+          <t>04. SA02CUX04 - Hisopado COVID-19 - Consulta y resultado</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -8114,7 +8114,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>01. TU01CUX01 - Turismo en BA</t>
+          <t>0. Core del bot (No tocar) [Tagear IA Off]</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
@@ -8140,7 +8140,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>02. DH11CUX02 Identidad de marca (estático)</t>
+          <t>EM03CUX02 Cursos virtuales - Academia BA Emprende</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
@@ -8153,20 +8153,20 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>CU10CUX02 Esquina Mafalda - Paseo de la historieta</t>
+          <t>DH11CUX03 Apertura QR keywords - Curso virtual de Identidad de Marca</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C593" s="6" t="n">
-        <v>4.462456541758451e-06</v>
+        <v>4.868134409191038e-06</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>18. Lactancia</t>
+          <t>01. TU01CUX01 - Turismo en BA</t>
         </is>
       </c>
       <c r="B594" s="5" t="n">
@@ -8179,7 +8179,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>SA08CUX01 Buscar hospitales - Donación de sangre ??</t>
+          <t>18. Lactancia</t>
         </is>
       </c>
       <c r="B595" s="5" t="n">
@@ -8192,7 +8192,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>SUA01CUX20 Apertura - Electricidad y agua</t>
+          <t>06. CIU05CUX06 Búsqueda de farmacias</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
@@ -8205,7 +8205,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>06. CIU05CUX06 Búsqueda de farmacias</t>
+          <t>SUA01CUX20 Apertura - Electricidad y agua</t>
         </is>
       </c>
       <c r="B597" s="5" t="n">
@@ -8218,20 +8218,20 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>DH11CUX03 Apertura QR keywords - Curso virtual de Identidad de Marca</t>
+          <t>SA08CUX01 Buscar hospitales - Donación de sangre 🩸</t>
         </is>
       </c>
       <c r="B598" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C598" s="6" t="n">
-        <v>4.462456541758451e-06</v>
+        <v>4.056778674325865e-06</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Niñez  - Uso del celular</t>
+          <t>07. MO04CUX07 - Permitido estacionar</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
@@ -8244,7 +8244,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Validar datos - Identidad de Género</t>
+          <t>05. EDU03CUX05 - Universidad de la Ciudad</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
@@ -8257,7 +8257,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>CU01CUX08 Apertura - BAM Fan de la Cultura</t>
+          <t>AI Otorgamiento [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
@@ -8283,7 +8283,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>07. MO04CUX07 - Permitido estacionar</t>
+          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
@@ -8296,7 +8296,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>AI Otorgamiento [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>CU01CUX08 Apertura - BAM Fan de la Cultura</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
@@ -8322,7 +8322,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>TR03CUX09 Apertura - Ambiente y EP</t>
+          <t>DH08CUX02 Apertura QR keywords - Curso virtual de Educación Financiera</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
@@ -8335,7 +8335,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CU01CUX15 Comienzo - Cabras Pista 1 - MIJU experiencia interactiva</t>
+          <t>TUR01CUX03 Validar datos - Identidad de Género</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
@@ -8348,7 +8348,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CU01CUX07 Apertura - BAM Con niños y niñas</t>
+          <t>TR04CUX41 Símbolo internacional de acceso - Trámites Nación</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
@@ -8361,7 +8361,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>14. TR04CUX14 - Certificado de Pobreza</t>
+          <t>11. SUA01CUX11 - Extracción de árbol</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
@@ -8374,7 +8374,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>05. EDU03CUX05 - Universidad de la Ciudad</t>
+          <t>33. TR04CUX33 - Permiso de espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
@@ -8387,7 +8387,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>11. SUA01CUX11 - Extracción de árbol</t>
+          <t>CU01CUX07 Apertura - BAM Con niños y niñas</t>
         </is>
       </c>
       <c r="B611" s="5" t="n">
@@ -8400,7 +8400,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>TR04CUX41 Símbolo internacional de acceso - Trámites Nación</t>
+          <t>Test [Test IABA Feedback]</t>
         </is>
       </c>
       <c r="B612" s="5" t="n">
@@ -8413,7 +8413,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>INN10CUX15 Error de servicio - Agente Donde Estacionar</t>
+          <t>EP04CUX01 Apertura web - Ecopuntos</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
@@ -8426,7 +8426,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Test [Test IABA Feedback]</t>
+          <t>14. TR04CUX14 - Certificado de Pobreza</t>
         </is>
       </c>
       <c r="B614" s="5" t="n">
@@ -8439,33 +8439,33 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>DH09CUX02 Clases y talleres - Programa Adolescencia</t>
+          <t>INN10CUX15 Error de servicio - Agente Donde Estacionar</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C615" s="6" t="n">
-        <v>3.245422939460692e-06</v>
+        <v>3.651100806893278e-06</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>TR03CUX28 CUIT - Nación</t>
+          <t>INN10CUX09 Preapertura - Experiencia accesibilidad PI</t>
         </is>
       </c>
       <c r="B616" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C616" s="6" t="n">
-        <v>3.245422939460692e-06</v>
+        <v>3.651100806893278e-06</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>DH11CUX08 Apertura - Compras con impacto</t>
+          <t>DH09CUX02 Clases y talleres - Programa Adolescencia</t>
         </is>
       </c>
       <c r="B617" s="5" t="n">
@@ -8478,7 +8478,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>DH11CUX08 Video 1 - Compras con impacto</t>
+          <t>DH05CUX01 Hablar con alguien - Adicciones</t>
         </is>
       </c>
       <c r="B618" s="5" t="n">
@@ -8491,7 +8491,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>DH05CUX01 Hablar con alguien - Adicciones</t>
+          <t>DH11CUX08 Apertura - Compras con impacto</t>
         </is>
       </c>
       <c r="B619" s="5" t="n">
@@ -8504,7 +8504,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>DEC05CUX02 Apertura - Impulsate a vos y a tu negocio</t>
+          <t>GE03CUX02 TrabajoBA - Autonomía económica</t>
         </is>
       </c>
       <c r="B620" s="5" t="n">
@@ -8517,7 +8517,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>14. TR04CUX14 - Certificado de Pobreza</t>
+          <t>04. TR04CUX04 - Registro de artistas callejeros</t>
         </is>
       </c>
       <c r="B621" s="5" t="n">
@@ -8530,7 +8530,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>EM03CUX02 Cursos virtuales - Academia BA Emprende</t>
+          <t>TR01CUX03 Cómo hacer el trámite - Solicitud de copia de planos de mensura, horizontalidad, prehorizontalidad y catastro</t>
         </is>
       </c>
       <c r="B622" s="5" t="n">
@@ -8543,20 +8543,20 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>DH08CUX02 Apertura QR keywords - Curso virtual de Educación Financiera</t>
+          <t>14. TR04CUX14 - Certificado de Pobreza</t>
         </is>
       </c>
       <c r="B623" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C623" s="6" t="n">
-        <v>3.245422939460692e-06</v>
+        <v>2.839745072028106e-06</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura - Subsecretaría de Deportes</t>
+          <t>VI01CUX01 Pagar tu crédito - Programa Viviendas IVC</t>
         </is>
       </c>
       <c r="B624" s="5" t="n">
@@ -8569,7 +8569,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>GE03CUX02 Apertura - Autonomía económica</t>
+          <t>EDU03CUX10 Apertura - Premio Docente</t>
         </is>
       </c>
       <c r="B625" s="5" t="n">
@@ -8582,7 +8582,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>DH11CUX03  Apertura estático principal - Curso virtual de Identidad de Marca</t>
+          <t>DEC05CUX02 Cómo participo - Impulsate a vos y a tu negocio</t>
         </is>
       </c>
       <c r="B626" s="5" t="n">
@@ -8595,7 +8595,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>33. TR04CUX33 - Permiso de espectáculos musicales en vivo</t>
+          <t>CU02CUX02 Apertura - Teatro Colón</t>
         </is>
       </c>
       <c r="B627" s="5" t="n">
@@ -8608,7 +8608,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>TU03CUX09 Qué hay para hacer - Planetario</t>
+          <t>DH11CUX03  Apertura estático principal - Curso virtual de Identidad de Marca</t>
         </is>
       </c>
       <c r="B628" s="5" t="n">
@@ -8621,7 +8621,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>18. TR04CUX18 - Clausura de local, obra o ascensor</t>
+          <t>TU03CUX01 Boca Juniors - Estadios de fútbol</t>
         </is>
       </c>
       <c r="B629" s="5" t="n">
@@ -8634,7 +8634,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>CU10CUX02 El Loco Chávez - Paseo de la historieta</t>
+          <t>18. TR04CUX18 - Clausura de local, obra o ascensor</t>
         </is>
       </c>
       <c r="B630" s="5" t="n">
@@ -8647,7 +8647,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>TU03CUX01 Boca Juniors - Estadios de fútbol</t>
+          <t>01. DH02CUX01 - RUPEPYS</t>
         </is>
       </c>
       <c r="B631" s="5" t="n">
@@ -8660,7 +8660,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>SE01CUX01 Apertura - Convocatoria de bomberos</t>
+          <t>CU01CUX15 Comienzo - Cabras Pista 1 - MIJU experiencia interactiva</t>
         </is>
       </c>
       <c r="B632" s="5" t="n">
@@ -8673,7 +8673,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>03. SA02CUX03 - Certificado COVID-19</t>
+          <t>CU10CUX02 El Loco Chávez - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B633" s="5" t="n">
@@ -8686,7 +8686,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>EDU03CUX10 Apertura - Premio Docente</t>
+          <t>TR03CUX09 Apertura - Ambiente y EP</t>
         </is>
       </c>
       <c r="B634" s="5" t="n">
@@ -8699,7 +8699,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Requisitos​ [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>TR01CUX09 Cómo hago el trámite - Certificado de Información Catastral</t>
         </is>
       </c>
       <c r="B635" s="5" t="n">
@@ -8712,7 +8712,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>VI01CUX01 Pagar tu crédito - Programa Viviendas IVC</t>
+          <t>28. TR04CUX28 - Registro de Establecimientos Gastronómicos</t>
         </is>
       </c>
       <c r="B636" s="5" t="n">
@@ -8725,7 +8725,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>CU01CUX09 Apertura - BAM Con amigos y amigas</t>
+          <t>03. SA02CUX03 - Certificado COVID-19</t>
         </is>
       </c>
       <c r="B637" s="5" t="n">
@@ -8738,7 +8738,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Apertura  - Uso del celular</t>
+          <t>CU01CUX14 Quiero ir - MIJU</t>
         </is>
       </c>
       <c r="B638" s="5" t="n">
@@ -8751,33 +8751,33 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>TR01CUX03 Cómo hacer el trámite - Solicitud de copia de planos de mensura, horizontalidad, prehorizontalidad y catastro</t>
+          <t>DEC05CUX02 Apertura - Impulsate a vos y a tu negocio</t>
         </is>
       </c>
       <c r="B639" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C639" s="6" t="n">
-        <v>2.839745072028106e-06</v>
+        <v>2.434067204595519e-06</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>CU02CUX02 Apertura - Teatro Colón</t>
+          <t>CU11CUX02 Qué propuestas hay - Programa Cultural en Barrios</t>
         </is>
       </c>
       <c r="B640" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C640" s="6" t="n">
-        <v>2.839745072028106e-06</v>
+        <v>2.434067204595519e-06</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>EDU05CUX06 Media y Superior - Profesorados</t>
+          <t>01. EM04CUX01 - BA PyMES y BA Empresas</t>
         </is>
       </c>
       <c r="B641" s="5" t="n">
@@ -8790,7 +8790,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>DH10CUX01 Monotributo - Trámites AFIP</t>
+          <t>GE03CUX02 Apertura - Autonomía económica</t>
         </is>
       </c>
       <c r="B642" s="5" t="n">
@@ -8803,7 +8803,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>EDU04CUX22 Maternales - Jardines de infantes</t>
+          <t>NI01CUX12 Botimisterios - Botimisterios</t>
         </is>
       </c>
       <c r="B643" s="5" t="n">
@@ -8816,7 +8816,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Apertura corta​ [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>TR03CUX16 Denuncia a administradores de consorcio - Defensa del consumidor</t>
         </is>
       </c>
       <c r="B644" s="5" t="n">
@@ -8829,7 +8829,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>MO10CUX01 Recorridos - Superapertura Metrobus</t>
+          <t>CU01CUX10 Apertura - BAM De paseo</t>
         </is>
       </c>
       <c r="B645" s="5" t="n">
@@ -8842,7 +8842,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>01. EM04CUX01 - BA PyMES y BA Empresas</t>
+          <t>DH11CUX04 Chat por Whatsapp - Curso Fotoproducto (estático)</t>
         </is>
       </c>
       <c r="B646" s="5" t="n">
@@ -8855,7 +8855,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>TR01CUX09 Cómo hago el trámite - Certificado de Información Catastral</t>
+          <t>EDU04CUX30 Apertura  - Uso del celular</t>
         </is>
       </c>
       <c r="B647" s="5" t="n">
@@ -8868,7 +8868,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>TR01CUX20 Qué necesito - Subsanación de Faltas Documentales</t>
+          <t>EDU05CUX06 Media y Superior - Profesorados</t>
         </is>
       </c>
       <c r="B648" s="5" t="n">
@@ -8881,7 +8881,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>EP04CUX01 Apertura web - Ecopuntos</t>
+          <t>CIU05CUX08 Sitios Históricos La Boca - Sitios históricos</t>
         </is>
       </c>
       <c r="B649" s="5" t="n">
@@ -8894,7 +8894,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CU01CUX10 Apertura - BAM De paseo</t>
+          <t>EDU04CUX22 Buscar un jardín - Jardines de infantes</t>
         </is>
       </c>
       <c r="B650" s="5" t="n">
@@ -8907,7 +8907,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>CU11CUX02 Qué propuestas hay - Programa Cultural en Barrios</t>
+          <t>22. TR04CUX22 - Fotocopia de Documentación Archivada</t>
         </is>
       </c>
       <c r="B651" s="5" t="n">
@@ -8920,7 +8920,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>28. TR04CUX28 - Registro de Establecimientos Gastronómicos</t>
+          <t>VI01CUX06 Apertura - Refacción + Fácil</t>
         </is>
       </c>
       <c r="B652" s="5" t="n">
@@ -8933,33 +8933,33 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>22. TR04CUX22 - Fotocopia de Documentación Archivada</t>
+          <t>01. CIU02CUX01 - Comunas de la Ciudad</t>
         </is>
       </c>
       <c r="B653" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C653" s="6" t="n">
-        <v>2.434067204595519e-06</v>
+        <v>2.028389337162932e-06</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>NI01CUX12 Botimisterios - Botimisterios</t>
+          <t>AGC01CUX02 Libro Digital - Inspecciones</t>
         </is>
       </c>
       <c r="B654" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C654" s="6" t="n">
-        <v>2.434067204595519e-06</v>
+        <v>2.028389337162932e-06</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>​​DH05CUX01 Más teléfonos​  [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>SE01CUX07 Apertura - Policía: reconocimiento facial</t>
         </is>
       </c>
       <c r="B655" s="5" t="n">
@@ -8972,7 +8972,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>NI01CUX01 Superapertura Boticlásicos - Boticuentos (granapertura) ??</t>
+          <t>CU01CUX09 Apertura - BAM Con amigos y amigas</t>
         </is>
       </c>
       <c r="B656" s="5" t="n">
@@ -8985,7 +8985,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>CU10CUX02 Diógenes y el Linyera - Paseo de la historieta</t>
+          <t>SUA01CUX08 Cargar foto 1 - Mejora de Barrido</t>
         </is>
       </c>
       <c r="B657" s="5" t="n">
@@ -8998,7 +8998,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>04. AM04CUX04 - Paseo Ambiental del Sur</t>
+          <t>DDHH03CUX02 Quiero adoptar - Adopción GCBA</t>
         </is>
       </c>
       <c r="B658" s="5" t="n">
@@ -9011,7 +9011,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>INN10CUX09 Preapertura - Experiencia accesibilidad PI</t>
+          <t>04. AM04CUX04 - Paseo Ambiental del Sur</t>
         </is>
       </c>
       <c r="B659" s="5" t="n">
@@ -9037,7 +9037,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>VI03CUX01  Quién puede pedirlo - Créditos Hipotecarios</t>
+          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
         </is>
       </c>
       <c r="B661" s="5" t="n">
@@ -9050,7 +9050,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>SUA01CUX08 Cargar foto 1 - Mejora de Barrido</t>
+          <t>MO06CUX03 Necesito ayuda - Pedaleá con Boti</t>
         </is>
       </c>
       <c r="B662" s="5" t="n">
@@ -9063,7 +9063,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Identificación Tardía</t>
+          <t>Niñez [NI] [NI01CUX01 Superapertura Boticlásicos]</t>
         </is>
       </c>
       <c r="B663" s="5" t="n">
@@ -9076,7 +9076,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>JU02CUX01 Hacer una consulta - Consejo de la Magistratura</t>
+          <t>01. DH05CUX01 - Adicciones</t>
         </is>
       </c>
       <c r="B664" s="5" t="n">
@@ -9089,7 +9089,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>AGC01CUX02 Libro Digital - Inspecciones</t>
+          <t>CU10CUX02 Diógenes y el Linyera - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B665" s="5" t="n">
@@ -9102,7 +9102,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>TR02CUX04 Qué necesito - Regularización dominial</t>
+          <t>CU10CUX02 Esquina Mafalda - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B666" s="5" t="n">
@@ -9115,7 +9115,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos La Boca - Balvanera</t>
+          <t>TR03CUX09 Denuncia vinculada con residuos patológicos - Ambiente y EP</t>
         </is>
       </c>
       <c r="B667" s="5" t="n">
@@ -9128,7 +9128,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>15. TR04CUX15 - Certificado de residencia precaria</t>
+          <t>DH11CUX08 Introducción - Compras con impacto</t>
         </is>
       </c>
       <c r="B668" s="5" t="n">
@@ -9141,137 +9141,137 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>DEC05CUX02 De qué se trata - Impulsate a vos y a tu negocio</t>
+          <t>01. DH02CUX01 - RUPEPYS</t>
         </is>
       </c>
       <c r="B669" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C669" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>MO06CUX03 Necesito ayuda - Pedaleá con Boti</t>
+          <t>SA08CUX02 Quiero ser donante - Donación de órganos ❤️</t>
         </is>
       </c>
       <c r="B670" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C670" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>SE01CUX07 Apertura - Policía: reconocimiento facial</t>
+          <t>SE01CUX01 Apertura - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B671" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C671" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>TR03CUX16 Inscripción al registro de administradores de consorcio - Defensa del consumidor</t>
+          <t>CIU05CUX11 Apertura con pedido de barrio - Encuentro con vecinos</t>
         </is>
       </c>
       <c r="B672" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C672" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>TR03CUX09 Denuncia vinculada con residuos patológicos - Ambiente y EP</t>
+          <t>SE01CUX01 Quiero inscribirme - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B673" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C673" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>TR04CUX16 Cómo lo tramito - Certificado Negativo de Inscripción de Nacimiento</t>
+          <t>TR01CUX20 Qué necesito - Subsanación de Faltas Documentales</t>
         </is>
       </c>
       <c r="B674" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C674" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>01. CIU02CUX01 - Comunas de la Ciudad</t>
+          <t>DH11CUX05  Apertura estático principal - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B675" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C675" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>DH02CUX01 Capacitaciones - RUPEPYS</t>
+          <t>TR02CUX04 Qué necesito - Regularización dominial</t>
         </is>
       </c>
       <c r="B676" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C676" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>CU10CUX02 Apertura Mafalda - Paseo de la historieta</t>
+          <t>TR04CUX16 Cómo lo tramito - Certificado Negativo de Inscripción de Nacimiento</t>
         </is>
       </c>
       <c r="B677" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C677" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>VI01CUX06 Apertura - Refacción + Fácil</t>
+          <t>TU03CUX09 Qué hay para hacer - Planetario</t>
         </is>
       </c>
       <c r="B678" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C678" s="6" t="n">
-        <v>2.028389337162932e-06</v>
+        <v>1.622711469730346e-06</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>SUA01CUX33 Apertura - Consultas por el Expediente de catastro, obras, instalaciones y factibilidad</t>
+          <t>Filtro de segurización [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B679" s="5" t="n">
@@ -9284,7 +9284,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>MO10CUX06 Apertura - Metrobus 9 de julio</t>
+          <t>AI Renovación [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B680" s="5" t="n">
@@ -9297,7 +9297,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Filtro de segurización [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>33. TR04CUX33 - Permiso de espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B681" s="5" t="n">
@@ -9310,7 +9310,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Apertura con pedido de barrio - Encuentro con vecinos</t>
+          <t>SUA01CUX33 Apertura - Consultas por el Expediente de catastro, obras, instalaciones y factibilidad</t>
         </is>
       </c>
       <c r="B682" s="5" t="n">
@@ -9323,7 +9323,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>0. Core del bot (No tocar) [Inactividad del usuario: Turismo MSFT]</t>
+          <t>CIU02CUX02 Cronograma comuna - Más servicios en tu barrio</t>
         </is>
       </c>
       <c r="B683" s="5" t="n">
@@ -9336,7 +9336,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos Devoto - Balvanera</t>
+          <t>11 - Celular en escuelas</t>
         </is>
       </c>
       <c r="B684" s="5" t="n">
@@ -9349,7 +9349,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>GE03CUX02 TrabajoBA - Autonomía económica</t>
+          <t>0. Core del bot (No tocar) [Inactividad del usuario: Turismo MSFT]</t>
         </is>
       </c>
       <c r="B685" s="5" t="n">
@@ -9362,7 +9362,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>TR03CUX06 Servicios de salud para la prevención de zoonosis - Ministerio de salud - Otros trámites</t>
+          <t>JU03CUX01 Tengo una consulta - Patrocinio penal</t>
         </is>
       </c>
       <c r="B686" s="5" t="n">
@@ -9375,7 +9375,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Apertura - Study BA</t>
+          <t>AM04CUX05 Quiero ir - Reserva Ecológica</t>
         </is>
       </c>
       <c r="B687" s="5" t="n">
@@ -9388,7 +9388,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>DH11CUX08 Video 2 - Compras con impacto</t>
+          <t>TU03CUX14 Apertura - Plaza Benjamín Gould</t>
         </is>
       </c>
       <c r="B688" s="5" t="n">
@@ -9401,7 +9401,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>CIU02CUX02 Cronograma comuna - Más servicios en tu barrio</t>
+          <t>TU03CUX09 Shows en el domo - Planetario</t>
         </is>
       </c>
       <c r="B689" s="5" t="n">
@@ -9414,7 +9414,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>TR01CUX20 Cómo hago el trámite - Subsanación de Faltas Documentales</t>
+          <t>EDU04CUX30 Niñez  - Uso del celular</t>
         </is>
       </c>
       <c r="B690" s="5" t="n">
@@ -9427,7 +9427,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>SA16CUX02 Dosis de refuerzo - Sarampión</t>
+          <t>EDU04CUX19 Apertura - Minecraft: Escuelas Reinventando Buenos Aires</t>
         </is>
       </c>
       <c r="B691" s="5" t="n">
@@ -9440,7 +9440,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>TU03CUX14 Apertura - Plaza Benjamín Gould</t>
+          <t>01. DH02CUX01 - RUPEPYS</t>
         </is>
       </c>
       <c r="B692" s="5" t="n">
@@ -9453,7 +9453,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>DH07CUX01 Cómo anotarme  - Redes por la Inclusión</t>
+          <t>Identificación Tardía</t>
         </is>
       </c>
       <c r="B693" s="5" t="n">
@@ -9466,46 +9466,46 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>AM04CUX05 Quiero ir - Reserva Ecológica</t>
+          <t>22. TR04CUX22 - Fotocopia de Documentación Archivada</t>
         </is>
       </c>
       <c r="B694" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C694" s="6" t="n">
-        <v>1.622711469730346e-06</v>
+        <v>1.217033602297759e-06</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>11 - Celular en escuelas</t>
+          <t>EM04CUX01 Grabados - BA PyMES y BA Empresas</t>
         </is>
       </c>
       <c r="B695" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C695" s="6" t="n">
-        <v>1.622711469730346e-06</v>
+        <v>1.217033602297759e-06</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>AI Renovación [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>DH11CUX08 Video 2 - Compras con impacto</t>
         </is>
       </c>
       <c r="B696" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C696" s="6" t="n">
-        <v>1.622711469730346e-06</v>
+        <v>1.217033602297759e-06</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>DH01CUX04 Pregunta 2.1 - Encuesta Subsidio Habitacional 690</t>
+          <t>VI01CUX06 Sobre el programa - Refacción + Fácil</t>
         </is>
       </c>
       <c r="B697" s="5" t="n">
@@ -9518,7 +9518,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DEC05CUX02 Cómo participo - Impulsate a vos y a tu negocio</t>
+          <t>SA16CUX02 Dosis de refuerzo - Sarampión</t>
         </is>
       </c>
       <c r="B698" s="5" t="n">
@@ -9544,7 +9544,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>04. TR04CUX04 - Registro de artistas callejeros</t>
+          <t>EDU03CUX05 Cursos de posgrado - Universidad de la Ciudad</t>
         </is>
       </c>
       <c r="B700" s="5" t="n">
@@ -9557,7 +9557,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Test [test turno a otra persona]</t>
+          <t>TR01CUX09 Qué necesito - Certificado de Información Catastral</t>
         </is>
       </c>
       <c r="B701" s="5" t="n">
@@ -9570,7 +9570,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>CU11CUX02 Destacados - Programa Cultural en Barrios</t>
+          <t>EDU05CUX04 Apertura corta - Tecnicaturas de Salud</t>
         </is>
       </c>
       <c r="B702" s="5" t="n">
@@ -9583,7 +9583,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 FONDES​ [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>14. SUA01CUX14 - Reparación de Baches</t>
         </is>
       </c>
       <c r="B703" s="5" t="n">
@@ -9596,7 +9596,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>EDU03CUX05 Cursos de posgrado - Universidad de la Ciudad</t>
+          <t>EDU05CUX02 * Apertura - Study BA</t>
         </is>
       </c>
       <c r="B704" s="5" t="n">
@@ -9609,7 +9609,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>OB05CUX01 Número de expediente erróneo - Consulta DGROC</t>
+          <t>Test [test turno a otra persona]</t>
         </is>
       </c>
       <c r="B705" s="5" t="n">
@@ -9622,7 +9622,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Test [Nuevo ambiente Uli fechas]</t>
+          <t>INN10CUX14 Apertura - Agente BAC</t>
         </is>
       </c>
       <c r="B706" s="5" t="n">
@@ -9635,7 +9635,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>EM04CUX01 Grabados - BA PyMES y BA Empresas</t>
+          <t>DEC05CUX02 De qué se trata - Impulsate a vos y a tu negocio</t>
         </is>
       </c>
       <c r="B707" s="5" t="n">
@@ -9648,7 +9648,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>AM04CUX02 Jornada del talar  - Jardín Botánico</t>
+          <t>TR02CUX04 Cómo es el trámite - Regularización dominial</t>
         </is>
       </c>
       <c r="B708" s="5" t="n">
@@ -9661,7 +9661,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>SA08CUX01 Requisitos - Donación de sangre ??</t>
+          <t>DH11CUX08 Pedido de datos - Compras con impacto</t>
         </is>
       </c>
       <c r="B709" s="5" t="n">
@@ -9674,7 +9674,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>01. DEC03CUXO1 - Patrocinio BA</t>
+          <t>DH08CUX02 Pregunta V3M2 - Curso virtual de Educación Financiera</t>
         </is>
       </c>
       <c r="B710" s="5" t="n">
@@ -9687,7 +9687,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>TU03CUX02 Apertura - Bar la Biela</t>
+          <t>TR03CUX06 Servicios de salud para la prevención de zoonosis - Ministerio de salud - Otros trámites</t>
         </is>
       </c>
       <c r="B711" s="5" t="n">
@@ -9700,7 +9700,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>05. CIU05CUX05 Buscar Código Postal</t>
+          <t>DH01CUX04 Pregunta 2.1 - Encuesta Subsidio Habitacional 690</t>
         </is>
       </c>
       <c r="B712" s="5" t="n">
@@ -9713,7 +9713,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Quiero adoptar - Adopción GCBA</t>
+          <t>32. TR04CUX32 - Pasaporte</t>
         </is>
       </c>
       <c r="B713" s="5" t="n">
@@ -9726,7 +9726,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>05. Parque de la Ciudad</t>
+          <t>MO02CUX01 Apertura web - Servicio de Cercanía</t>
         </is>
       </c>
       <c r="B714" s="5" t="n">
@@ -9739,7 +9739,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DDHH03CUX05 Hacer una consulta - Observatorio SIPROID</t>
+          <t>CU11CUX02 Destacados - Programa Cultural en Barrios</t>
         </is>
       </c>
       <c r="B715" s="5" t="n">
@@ -9752,7 +9752,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VI03CUX01 Cómo funciona  - Créditos Hipotecarios</t>
+          <t>TU03CUX02 Apertura - Bar la Biela</t>
         </is>
       </c>
       <c r="B716" s="5" t="n">
@@ -9765,7 +9765,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>04. SA02CUX04 - Hisopado COVID-19 - Consulta y resultado</t>
+          <t>Test [Nuevo ambiente Uli fechas]</t>
         </is>
       </c>
       <c r="B717" s="5" t="n">
@@ -9778,7 +9778,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>32. TR04CUX32 - Pasaporte</t>
+          <t>Inspecciones Programadas - Problemas</t>
         </is>
       </c>
       <c r="B718" s="5" t="n">
@@ -9804,7 +9804,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DH02CUX01 Quiero anotarme - RUPEPYS</t>
+          <t>04. SA02CUX04 - Hisopado COVID-19 - Consulta y resultado</t>
         </is>
       </c>
       <c r="B720" s="5" t="n">
@@ -9817,7 +9817,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>JU03CUX01 Tengo una consulta - Patrocinio penal</t>
+          <t>TUR01CUX03 Por lugar &gt; No sirve - Identidad de Género</t>
         </is>
       </c>
       <c r="B721" s="5" t="n">
@@ -9830,124 +9830,124 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>CU01CUX14 Quiero ir - MIJU</t>
+          <t>TR03CUX07 Apertura - Subsecretaría de Deportes</t>
         </is>
       </c>
       <c r="B722" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C722" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>INN10CUX14 Apertura - Agente BAC</t>
+          <t>22. TR04CUX22 - Fotocopia de Documentación Archivada</t>
         </is>
       </c>
       <c r="B723" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C723" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>TUR01CUX14 Fecha de nacimiento - Turnera vacunación antigripal</t>
+          <t>CU10CUX02 Apertura Mafalda - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B724" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C724" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DH08CUX02 Responder pregunta V1M2 - Curso virtual de Educación Financiera</t>
+          <t>Test [Lucho Test Segmento]</t>
         </is>
       </c>
       <c r="B725" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C725" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DH11CUX05 Pedido de datos - Curso Fotoproducto virtual</t>
+          <t>02. Clubes de Barrio DE03CUX02</t>
         </is>
       </c>
       <c r="B726" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C726" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>EDU05CUX04 Apertura corta - Tecnicaturas de Salud</t>
+          <t>TUR01CUX03 Validación turno - Identidad de Género</t>
         </is>
       </c>
       <c r="B727" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C727" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Inspecciones Programadas - Problemas</t>
+          <t>JU02CUX01 Juzgados de turno - Consejo de la Magistratura</t>
         </is>
       </c>
       <c r="B728" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C728" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>EP04CUX01 Chat por WhatsApp - Ecopuntos</t>
+          <t>JU02CUX01 Hacer una consulta - Consejo de la Magistratura</t>
         </is>
       </c>
       <c r="B729" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C729" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>14. SUA01CUX14 - Reparación de Baches</t>
+          <t>TU01CUX05  Necesito ayuda - Seguridad turística</t>
         </is>
       </c>
       <c r="B730" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C730" s="6" t="n">
-        <v>1.217033602297759e-06</v>
+        <v>8.113557348651729e-07</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>MO10CUX02 Apertura - Metrobus del Bajo</t>
+          <t>DEC05CUX03 Apertura - Política energética para empresas</t>
         </is>
       </c>
       <c r="B731" s="5" t="n">
@@ -9960,7 +9960,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>MO10CUX03 Apertura - Metrobus del Norte</t>
+          <t>DH02CUX01 Oportunidades  - RUPEPYS</t>
         </is>
       </c>
       <c r="B732" s="5" t="n">
@@ -9973,7 +9973,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Respuestas TXT Gen [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>01. TU01CUX01 - Turismo en BA</t>
         </is>
       </c>
       <c r="B733" s="5" t="n">
@@ -9986,7 +9986,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>15. EDU04CUX15 - Escuelas públicas bilingües</t>
+          <t>01. Basílica del Pilar</t>
         </is>
       </c>
       <c r="B734" s="5" t="n">
@@ -9999,7 +9999,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DH02CUX01 Créditos emprendedores - RUPEPYS</t>
+          <t>TR05CUX04 Figura en el registro - Consulta de deudores morosos</t>
         </is>
       </c>
       <c r="B735" s="5" t="n">
@@ -10012,7 +10012,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>SA08CUX02 Tengo una consulta - Donación de órganos ??</t>
+          <t>DH02CUX01 Financiamiento - RUPEPYS</t>
         </is>
       </c>
       <c r="B736" s="5" t="n">
@@ -10025,7 +10025,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DEC05CUX03 Apertura - Política energética para empresas</t>
+          <t>NI01CUX10 Inicio del cuento - El tranvía loco de Caballito</t>
         </is>
       </c>
       <c r="B737" s="5" t="n">
@@ -10038,7 +10038,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>EDU05CUX06 Otros profesorados - Profesorados</t>
+          <t>Feedback unificado</t>
         </is>
       </c>
       <c r="B738" s="5" t="n">
@@ -10051,7 +10051,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>VI01CUX05 De qué se trata - Programa Ley 624</t>
+          <t>CIU05CUX08 El Castillito - Sitios históricos</t>
         </is>
       </c>
       <c r="B739" s="5" t="n">
@@ -10064,7 +10064,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>VI01CUX06 Cómo me postulo - Refacción + Fácil</t>
+          <t>Problema al ejecutar acciones de código [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B740" s="5" t="n">
@@ -10077,7 +10077,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>03. SA02CUX03 - Certificado COVID-19</t>
+          <t>EDU05CUX02 * Qué puedo estudiar (Estudio en BA) - Study BA</t>
         </is>
       </c>
       <c r="B741" s="5" t="n">
@@ -10090,7 +10090,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Problema al ejecutar acciones de código [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>01. SA02CUX01 - Coronavirus</t>
         </is>
       </c>
       <c r="B742" s="5" t="n">
@@ -10103,7 +10103,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>NI01CUX10 Inicio del cuento - El tranvía loco de Caballito</t>
+          <t>SUA01CUX27 No encontró ubicación - Mayor luminaria</t>
         </is>
       </c>
       <c r="B743" s="5" t="n">
@@ -10116,7 +10116,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Seleccionar hora - Por Lugar - Identidad de Género</t>
+          <t>Respuestas TXT Gen [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B744" s="5" t="n">
@@ -10129,7 +10129,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Por lugar &gt; No sirve - Identidad de Género</t>
+          <t>CU01CUX15 Las Cabras Macabras - MIJU experiencia interactiva</t>
         </is>
       </c>
       <c r="B745" s="5" t="n">
@@ -10142,7 +10142,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Elegir tipo de turrno - Identidad de Género</t>
+          <t>DDHH03CUX05 Hacer una consulta - Observatorio SIPROID</t>
         </is>
       </c>
       <c r="B746" s="5" t="n">
@@ -10155,7 +10155,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>01. Basílica del Pilar</t>
+          <t>MO10CUX06 Líneas - Metrobus 9 de julio</t>
         </is>
       </c>
       <c r="B747" s="5" t="n">
@@ -10168,7 +10168,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>NI01CUX05 Botimisiones - Boticuentos 2023: Superapertura y CC</t>
+          <t>MO10CUX06 Apertura - Metrobus 9 de julio</t>
         </is>
       </c>
       <c r="B748" s="5" t="n">
@@ -10181,7 +10181,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>NI01CUX09 Escenario - El fantasma del Anfiteatro</t>
+          <t>DH11CUX07 Introducción - Geolocalizacion virtual</t>
         </is>
       </c>
       <c r="B749" s="5" t="n">
@@ -10194,7 +10194,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>04. TR04CUX04 - Registro de artistas callejeros</t>
+          <t>TR01CUX20 Cómo hago el trámite - Subsanación de Faltas Documentales</t>
         </is>
       </c>
       <c r="B750" s="5" t="n">
@@ -10207,7 +10207,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>01. SA02CUX01 - Coronavirus</t>
+          <t>MO10CUX03 Líneas - Metrobus del Norte</t>
         </is>
       </c>
       <c r="B751" s="5" t="n">
@@ -10220,7 +10220,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>AM04CUX04 Visitas guiadas - Paseo Ambiental del Sur</t>
+          <t>NI01CUX09 Gran show en el Teatro Colón - El fantasma del Anfiteatro</t>
         </is>
       </c>
       <c r="B752" s="5" t="n">
@@ -10233,7 +10233,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>33. TR04CUX33 - Permiso de espectáculos musicales en vivo</t>
+          <t>CU01CUX09 Patio - BAM Con amigos y amigas</t>
         </is>
       </c>
       <c r="B753" s="5" t="n">
@@ -10246,7 +10246,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>EDU03CUX06 Cómo me anoto - Escuela de Maestros</t>
+          <t>CIU05CUX08 Sitios históricos Belgrano - Sitios históricos</t>
         </is>
       </c>
       <c r="B754" s="5" t="n">
@@ -10259,7 +10259,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>Test [Lucho Test Segmento]</t>
+          <t>SA08CUX01 Requisitos - Donación de sangre 🩸</t>
         </is>
       </c>
       <c r="B755" s="5" t="n">
@@ -10272,7 +10272,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>SE01CUX01 Proceso de Selección  - Convocatoria de bomberos</t>
+          <t>SE01CUX01 Cómo se cursa   - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B756" s="5" t="n">
@@ -10285,7 +10285,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>SE01CUX01 Quiero inscribirme - Convocatoria de bomberos</t>
+          <t>SE06CUX01  Buscar un sendero - Senderos escolares</t>
         </is>
       </c>
       <c r="B757" s="5" t="n">
@@ -10298,7 +10298,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>TR01CUX01 Requisitos - GESTIÓN PRIVADA ? CERT. DOCUMENTACIÓN DOCENTES</t>
+          <t>CIU05CUX10 Murales La Boca - La Boca</t>
         </is>
       </c>
       <c r="B758" s="5" t="n">
@@ -10311,7 +10311,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>TR03CUX25 Cómo pagar boletas - Ministerio de Desarrollo Urbano y Transporte - DGROC CATASTRO</t>
+          <t>EDU05CUX02 * Fechas claves (Estudio en BA) - Study BA</t>
         </is>
       </c>
       <c r="B759" s="5" t="n">
@@ -10324,7 +10324,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Cuestionario Flows - Encuentro con vecinos</t>
+          <t>04. TR04CUX04 - Registro de artistas callejeros</t>
         </is>
       </c>
       <c r="B760" s="5" t="n">
@@ -10337,7 +10337,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>DH11CUX08 Pedido de datos - Compras con impacto</t>
+          <t>DDHH01CUX01 Documentos - Guía Migrante</t>
         </is>
       </c>
       <c r="B761" s="5" t="n">
@@ -10350,7 +10350,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>DH11CUX07 Video 1 - Geolocalizacion virtual</t>
+          <t>TR01CUX01 Requisitos - GESTIÓN PRIVADA – CERT. DOCUMENTACIÓN DOCENTES</t>
         </is>
       </c>
       <c r="B762" s="5" t="n">
@@ -10363,7 +10363,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Murales La Boca - Caballito</t>
+          <t>Derivación a agente de BA Taxi</t>
         </is>
       </c>
       <c r="B763" s="5" t="n">
@@ -10376,7 +10376,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios históricos Belgrano - Balvanera</t>
+          <t>03. SA02CUX03 - Certificado COVID-19</t>
         </is>
       </c>
       <c r="B764" s="5" t="n">
@@ -10389,7 +10389,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>Feedback unificado</t>
+          <t>02. MO06CUX02 - Ecobici</t>
         </is>
       </c>
       <c r="B765" s="5" t="n">
@@ -10402,7 +10402,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>TR05CUX04 Figura en el registro - Consulta de deudores morosos</t>
+          <t>TUR01CUX14 Nombre y apellido - Turnera vacunación antigripal</t>
         </is>
       </c>
       <c r="B766" s="5" t="n">
@@ -10415,7 +10415,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos Caballito - Balvanera</t>
+          <t>Hablar con operador [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B767" s="5" t="n">
@@ -10428,7 +10428,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>DDHH03CUX01 Chicos perdidos - Bifurcador Derechos de Niños_as y Adolescentes</t>
+          <t>VI03CUX01 Primera casa - Créditos Hipotecarios</t>
         </is>
       </c>
       <c r="B768" s="5" t="n">
@@ -10441,7 +10441,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>GE03CUX02 Quiero capacitarme - Autonomía económica</t>
+          <t>Derivación a agente de SIGEHOS</t>
         </is>
       </c>
       <c r="B769" s="5" t="n">
@@ -10454,7 +10454,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Murales Mujeres - Balvanera</t>
+          <t>CU10CUX02 Clemente &gt; Contame más - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B770" s="5" t="n">
@@ -10467,215 +10467,215 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>DH11CUX05  Apertura estático principal - Curso Fotoproducto virtual</t>
+          <t>OB05CUX01 Número de expediente erróneo - Consulta DGROC</t>
         </is>
       </c>
       <c r="B771" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C771" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>TR01CUX18 Pedí la constancia - Solicitud de antecedentes de habilitaciones</t>
+          <t>OB05CUX01 Otro estado - 6A - Consulta DGROC</t>
         </is>
       </c>
       <c r="B772" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C772" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>TR01CUX09 Qué necesito - Certificado de Información Catastral</t>
+          <t>OB05CUX01 Tramitación registro Plano obra civil - 2B - Consulta DGROC</t>
         </is>
       </c>
       <c r="B773" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C773" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>02. Clubes de Barrio DE03CUX02</t>
+          <t>0. Core del bot (No tocar) [Destagear UsuarioPrueba]</t>
         </is>
       </c>
       <c r="B774" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C774" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>TR01CUX15 Requisitos - TAD Registro de Empleadores</t>
+          <t>DH11CUX08 Video 2 Pregunta 1 - Compras con impacto</t>
         </is>
       </c>
       <c r="B775" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C775" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>INN01CUX01 Gaming labs - Superapertura BA Gaming</t>
+          <t>05. CIU05CUX05 Buscar Código Postal</t>
         </is>
       </c>
       <c r="B776" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C776" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>Hablar con operador [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>CU01CUX10 BA Punto de partida - BAM De paseo</t>
         </is>
       </c>
       <c r="B777" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C777" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>TR02CUX04 Cómo es el trámite - Regularización dominial</t>
+          <t>Test STT pia</t>
         </is>
       </c>
       <c r="B778" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C778" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>EDU04CUX19 Apertura - Minecraft: Escuelas Reinventando Buenos Aires</t>
+          <t>05. Parque de la Ciudad</t>
         </is>
       </c>
       <c r="B779" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C779" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>Derivación a agente de BA Taxi</t>
+          <t>EP04CUX01 Secos - Ecopuntos</t>
         </is>
       </c>
       <c r="B780" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C780" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>DH08CUX02 Pregunta V1M3 - Curso virtual de Educación Financiera</t>
+          <t>EM04CUX02 Tipos de crédito mujeres emprendedoras - Mujer Emprendedora</t>
         </is>
       </c>
       <c r="B781" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C781" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Estudio en BA - Study BA</t>
+          <t>CIU05CUX08 Murales Mujeres - Sitios históricos</t>
         </is>
       </c>
       <c r="B782" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C782" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>VI03CUX01 Primera casa - Créditos Hipotecarios</t>
+          <t>CIU05CUX08 Escuela de Floricultura - Sitios históricos</t>
         </is>
       </c>
       <c r="B783" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C783" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>VI01CUX06 Sobre el programa - Refacción + Fácil</t>
+          <t>CIU05CUX08 Barrio Inglés - Sitios históricos</t>
         </is>
       </c>
       <c r="B784" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C784" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>03. AM03CUX03 - Red de Refugios Climáticos</t>
+          <t>TR01CUX03 Requisitos - Solicitud de copia de planos de mensura, horizontalidad, prehorizontalidad y catastro</t>
         </is>
       </c>
       <c r="B785" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C785" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>02. MO06CUX02 - Ecobici</t>
+          <t>CU01CUX15 Mr. M  - MIJU experiencia interactiva</t>
         </is>
       </c>
       <c r="B786" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C786" s="6" t="n">
-        <v>8.113557348651729e-07</v>
+        <v>4.056778674325865e-07</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>a [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>EDU04CUX30 Primera infancia  - Uso del celular</t>
         </is>
       </c>
       <c r="B787" s="5" t="n">
@@ -10688,7 +10688,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>fulfilled of Insulto [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>DDHH03CUX01 Chicos perdidos - Bifurcador Derechos de Niños_as y Adolescentes</t>
         </is>
       </c>
       <c r="B788" s="5" t="n">
@@ -10701,7 +10701,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>fulfilled of Otro Tramite [NOMBRE AMIGABLE FALTANTE]</t>
+          <t>EDU04CUX29 Horarios - Vacaciones en la escuela</t>
         </is>
       </c>
       <c r="B789" s="5" t="n">
@@ -10714,7 +10714,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>AM03CUX04 Cuidados del agua - Ambiente</t>
+          <t>EDU04CUX30 Celu en el aula - Uso del celular</t>
         </is>
       </c>
       <c r="B790" s="5" t="n">
@@ -10727,7 +10727,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Fechas claves (Estudio en BA) - Study BA</t>
+          <t>SUA01CUX21 Subir foto 3 - Reubicación de contenedores</t>
         </is>
       </c>
       <c r="B791" s="5" t="n">
@@ -10740,7 +10740,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>DH08CUX02 Sí, dale V3M1 - Curso virtual de Educación Financiera</t>
+          <t>SUA01CUX15 Dirección - Desagote de pozo ciego</t>
         </is>
       </c>
       <c r="B792" s="5" t="n">
@@ -10753,7 +10753,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>03. DH11CUX03 Curso virtual de Identidad de Marca</t>
+          <t>07. CO08CUX7 - Pista Parque Sarmiento</t>
         </is>
       </c>
       <c r="B793" s="5" t="n">
@@ -10766,7 +10766,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>03. DH11CUX03 Curso virtual de Identidad de Marca</t>
+          <t>Denunciar ahora</t>
         </is>
       </c>
       <c r="B794" s="5" t="n">
@@ -10779,7 +10779,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura Inscripción al registro público de salvavidas - Subsecretaría de Deportes</t>
+          <t>13. SUA01CUX13 - Falta de conservación de fachada</t>
         </is>
       </c>
       <c r="B795" s="5" t="n">
@@ -10792,7 +10792,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>TR03CUX08 Registro Nacional de Productos Alimenticios (RNPA) / Registro Nacional de Establecimientos (RNE) - AGC</t>
+          <t>CU01CUX07 Ciudades imaginadas - BAM Con niños y niñas</t>
         </is>
       </c>
       <c r="B796" s="5" t="n">
@@ -10805,7 +10805,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>DH11CUX04 Chat por Whatsapp - Curso Fotoproducto (estático)</t>
+          <t>28. TR04CUX28 - Registro de Establecimientos Gastronómicos</t>
         </is>
       </c>
       <c r="B797" s="5" t="n">
@@ -10818,7 +10818,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>DH11CUX05  Apertura de contingencia I - Curso Fotoproducto virtual</t>
+          <t>CU01CUX08 BA en construcción - BAM Fan de la Cultura</t>
         </is>
       </c>
       <c r="B798" s="5" t="n">
@@ -10831,7 +10831,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>DH11CUX05 Repaso V1 - Curso Fotoproducto virtual</t>
+          <t>SE01CUX01 Proceso de Selección  - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B799" s="5" t="n">
@@ -10844,7 +10844,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>DH11CUX05 Responde bien V1 - Curso Fotoproducto virtual</t>
+          <t>SE01CUX01 Qué necesito - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B800" s="5" t="n">
@@ -10857,7 +10857,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>DH11CUX05 Silencio user - Curso Fotoproducto virtual</t>
+          <t>SE01CUX04 Recomendaciones - Bomberos</t>
         </is>
       </c>
       <c r="B801" s="5" t="n">
@@ -10870,7 +10870,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>DH11CUX05 V1 - Curso Fotoproducto virtual</t>
+          <t>CIU05CUX12 Envío exitoso - Agentes en Calle</t>
         </is>
       </c>
       <c r="B802" s="5" t="n">
@@ -10883,7 +10883,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>DH11CUX07 Apertura - Geolocalizacion virtual</t>
+          <t>CIU05CUX11 Error de envío - Encuentro con vecinos</t>
         </is>
       </c>
       <c r="B803" s="5" t="n">
@@ -10896,7 +10896,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>DH11CUX07 Validación de datos - Geolocalizacion virtual</t>
+          <t>CIU05CUX11 Encuesta de satisfacción - Encuentro con vecinos</t>
         </is>
       </c>
       <c r="B804" s="5" t="n">
@@ -10909,7 +10909,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>CIU02CUX02 Info de los servicios - Más servicios en tu barrio</t>
+          <t>CIU05CUX11 Cuestionario Flows - Encuentro con vecinos</t>
         </is>
       </c>
       <c r="B805" s="5" t="n">
@@ -10922,7 +10922,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>00. Deporte Adaptado</t>
+          <t>CIU05CUX08 Palacio Hirsch - Sitios históricos</t>
         </is>
       </c>
       <c r="B806" s="5" t="n">
@@ -10935,7 +10935,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>GE02CUX02 Realidad histórica - Historia del 8M</t>
+          <t>SE01CUX07 Cómo funciona - Policía: reconocimiento facial</t>
         </is>
       </c>
       <c r="B807" s="5" t="n">
@@ -10948,7 +10948,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>TR02CUX05 Qué necesito - Entrega de Certificados Escolares para Ciudadanía Porteña-</t>
+          <t>DDHH03CUX09 Qué necesito - Programa Abrazar</t>
         </is>
       </c>
       <c r="B808" s="5" t="n">
@@ -10961,7 +10961,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>TR02CUX05 Validar datos - Entrega de Certificados Escolares para Ciudadanía Porteña-</t>
+          <t>VI01CUX06 Qué necesito - Refacción + Fácil</t>
         </is>
       </c>
       <c r="B809" s="5" t="n">
@@ -10974,7 +10974,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>Derivación a agente de 147</t>
+          <t>VI01CUX06 Cómo me postulo - Refacción + Fácil</t>
         </is>
       </c>
       <c r="B810" s="5" t="n">
@@ -10987,7 +10987,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>IN01CUX01 Audiencia virtual - Infracciones, Derivación a agente de Infracciones</t>
+          <t>01. DH02CUX01 - RUPEPYS</t>
         </is>
       </c>
       <c r="B811" s="5" t="n">
@@ -11000,7 +11000,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>0. Core del bot (No tocar) [Destagear UsuarioPrueba]</t>
+          <t>TUR01CUX14 Fecha de nacimiento - Turnera vacunación antigripal</t>
         </is>
       </c>
       <c r="B812" s="5" t="n">
@@ -11013,7 +11013,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>TR01CUX08 Qué necesito - Certificación Documentación Institución Activa</t>
+          <t>03. AM03CUX03 - Red de Refugios Climáticos</t>
         </is>
       </c>
       <c r="B813" s="5" t="n">
@@ -11026,7 +11026,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>CIU05CUX11 Encuesta de satisfacción - Encuentro con vecinos</t>
+          <t>Cambiar datos DNI</t>
         </is>
       </c>
       <c r="B814" s="5" t="n">
@@ -11039,7 +11039,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>CIU05CUX12 Envío exitoso - Agentes en Calle</t>
+          <t>fulfilled of Otro Tramite [NOMBRE AMIGABLE FALTANTE]</t>
         </is>
       </c>
       <c r="B815" s="5" t="n">
@@ -11052,7 +11052,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>DH11CUX08 Validación de datos - Compras con impacto</t>
+          <t>CIU05CUX08 Sitios Históricos Devoto - Sitios históricos</t>
         </is>
       </c>
       <c r="B816" s="5" t="n">
@@ -11065,7 +11065,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>GE03CUX02 Integración laboral - Autonomía económica</t>
+          <t>CIU05CUX08 Otros sitios Caballito - Sitios históricos</t>
         </is>
       </c>
       <c r="B817" s="5" t="n">
@@ -11078,7 +11078,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>GE03CUX02 Soy emprendedora - Autonomía económica</t>
+          <t>SA13CUX01 Contacto  - Cursos RCP y Primeros Auxilios</t>
         </is>
       </c>
       <c r="B818" s="5" t="n">
@@ -11091,7 +11091,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>TR03CUX25 Estado de mi trámite - Ministerio de Desarrollo Urbano y Transporte - DGROC CATASTRO</t>
+          <t>EDU03CUX06 Cómo funciona - Escuela de Maestros</t>
         </is>
       </c>
       <c r="B819" s="5" t="n">
@@ -11104,7 +11104,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>TR03CUX27 Retiro del vehículo acarreado abandonado - Ministerio de Justicia y Seguridad</t>
+          <t>EDU03CUX06 Hacer una consulta - Escuela de Maestros</t>
         </is>
       </c>
       <c r="B820" s="5" t="n">
@@ -11117,7 +11117,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>EP04CUX01 Secos - Ecopuntos</t>
+          <t>SE01CUX01 Apertura corta - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B821" s="5" t="n">
@@ -11130,7 +11130,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Primera infancia  - Uso del celular</t>
+          <t>SE01CUX01 Documentación  - Convocatoria de bomberos</t>
         </is>
       </c>
       <c r="B822" s="5" t="n">
@@ -11143,7 +11143,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Barrio Inglés - Balvanera</t>
+          <t>CIU05CUX08 San Diego La Boca - Sitios históricos</t>
         </is>
       </c>
       <c r="B823" s="5" t="n">
@@ -11156,7 +11156,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Palacio Hirsch - Balvanera</t>
+          <t>CIU05CUX08 Sitios Históricos Caballito - Sitios históricos</t>
         </is>
       </c>
       <c r="B824" s="5" t="n">
@@ -11169,7 +11169,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Puente transbordador - Balvanera</t>
+          <t>SA08CUX01 Campañas de donación - Donación de sangre 🩸</t>
         </is>
       </c>
       <c r="B825" s="5" t="n">
@@ -11182,7 +11182,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>SE06CUX01  Buscar un sendero - Senderos escolares</t>
+          <t>CIU02CUX02 Denuncias y reclamos - Más servicios en tu barrio</t>
         </is>
       </c>
       <c r="B826" s="5" t="n">
@@ -11195,7 +11195,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>SE06CUX01 Cómo comunicarme - Senderos escolares</t>
+          <t>DH11CUX05 Pedido de datos - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B827" s="5" t="n">
@@ -11208,7 +11208,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>CO12CUX02 Número de emergencia - Temporal en BA</t>
+          <t>DH11CUX05 Responder pregunta V1 - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B828" s="5" t="n">
@@ -11221,7 +11221,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>SUA01CUX15 Dirección - Desagote de pozo ciego</t>
+          <t>DH11CUX05  Apertura de contingencia I - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B829" s="5" t="n">
@@ -11234,7 +11234,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>SUA01CUX21 Subir foto 3 - Reubicación de contenedores</t>
+          <t>DH11CUX07 Pedido de datos - Geolocalizacion virtual</t>
         </is>
       </c>
       <c r="B830" s="5" t="n">
@@ -11247,7 +11247,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>EDU04CUX29 Horarios - Vacaciones en la escuela</t>
+          <t>TR02CUX05 Validar datos - Entrega de Certificados Escolares para Ciudadanía Porteña-</t>
         </is>
       </c>
       <c r="B831" s="5" t="n">
@@ -11260,7 +11260,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Celu en el aula - Uso del celular</t>
+          <t>DH11CUX05 Encuesta - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B832" s="5" t="n">
@@ -11273,7 +11273,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Denunciar ahora</t>
+          <t>DH11CUX05 V4 - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B833" s="5" t="n">
@@ -11299,7 +11299,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DDHH03CUX09 De qué se trata - Programa Abrazar</t>
+          <t>MO06CUX03 Más de bicis en BA - Pedaleá con Boti</t>
         </is>
       </c>
       <c r="B835" s="5" t="n">
@@ -11312,7 +11312,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 1 - Encuesta BAX</t>
+          <t>MO06CUX03 Circular en BA  - Pedaleá con Boti</t>
         </is>
       </c>
       <c r="B836" s="5" t="n">
@@ -11325,7 +11325,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>CU01CUX08 BA en construcción - BAM Fan de la Cultura</t>
+          <t>03. DH11CUX03 Curso virtual de Identidad de Marca</t>
         </is>
       </c>
       <c r="B837" s="5" t="n">
@@ -11338,7 +11338,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>CU01CUX10 BA Punto de partida - BAM De paseo</t>
+          <t>03. DH11CUX03 Curso virtual de Identidad de Marca</t>
         </is>
       </c>
       <c r="B838" s="5" t="n">
@@ -11351,7 +11351,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>CU01CUX15 Las Cabras Macabras - MIJU experiencia interactiva</t>
+          <t>MO10CUX04 Combinaciones - Metrobus Juan B. Justo</t>
         </is>
       </c>
       <c r="B839" s="5" t="n">
@@ -11364,7 +11364,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>JU03CUX01 Cómo funciona - Patrocinio penal</t>
+          <t>MO10CUX08 Apertura - Metrobus Alberdi-Directorio</t>
         </is>
       </c>
       <c r="B840" s="5" t="n">
@@ -11377,7 +11377,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>JU03CUX01 Qué necesito - Patrocinio penal</t>
+          <t>BX02CUX01 Pregunta 1 - Encuesta BAX</t>
         </is>
       </c>
       <c r="B841" s="5" t="n">
@@ -11390,7 +11390,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>SE01CUX01 Documentación  - Convocatoria de bomberos</t>
+          <t>MO10CUX04 Apertura - Metrobus Juan B. Justo</t>
         </is>
       </c>
       <c r="B842" s="5" t="n">
@@ -11403,7 +11403,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>SE01CUX07 Cómo funciona - Policía: reconocimiento facial</t>
+          <t>MO10CUX04 Puntos de interés - Metrobus Juan B. Justo</t>
         </is>
       </c>
       <c r="B843" s="5" t="n">
@@ -11416,7 +11416,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>CU01CUX07 Ciudades imaginadas - BAM Con niños y niñas</t>
+          <t>MO09CUX04 Obra hidráulica - Autopista Dellepiane</t>
         </is>
       </c>
       <c r="B844" s="5" t="n">
@@ -11429,7 +11429,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>NI01CUX03  A Lector - Super chanchitos ??????</t>
+          <t>MO10CUX01 Info para viajar - Superapertura Metrobus</t>
         </is>
       </c>
       <c r="B845" s="5" t="n">
@@ -11442,7 +11442,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>MO06CUX01 Bicicleterías - Ciclovías</t>
+          <t>MO10CUX01 Recorridos - Superapertura Metrobus</t>
         </is>
       </c>
       <c r="B846" s="5" t="n">
@@ -11455,7 +11455,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>MO06CUX03 Circular en BA  - Pedaleá con Boti</t>
+          <t>MO10CUX02 Apertura - Metrobus del Bajo</t>
         </is>
       </c>
       <c r="B847" s="5" t="n">
@@ -11468,7 +11468,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>MO06CUX03 Más de bicis en BA - Pedaleá con Boti</t>
+          <t>MO10CUX02 Líneas - Metrobus del Bajo</t>
         </is>
       </c>
       <c r="B848" s="5" t="n">
@@ -11481,7 +11481,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>SA13CUX01 Contacto  - Cursos RCP y Primeros Auxilios</t>
+          <t>MO10CUX03 Apertura - Metrobus del Norte</t>
         </is>
       </c>
       <c r="B849" s="5" t="n">
@@ -11494,7 +11494,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>SE01CUX01 Apertura corta - Convocatoria de bomberos</t>
+          <t>NI01CUX10 En un viaje inesperado - El tranvía loco de Caballito</t>
         </is>
       </c>
       <c r="B850" s="5" t="n">
@@ -11507,7 +11507,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>SE01CUX01 Cómo se cursa   - Convocatoria de bomberos</t>
+          <t>NI01CUX09 Subir a la calesita - El fantasma del Anfiteatro</t>
         </is>
       </c>
       <c r="B851" s="5" t="n">
@@ -11520,7 +11520,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>01. TU01CUX01 - Turismo en BA</t>
+          <t>TR03CUX25 Estado de mi trámite - Ministerio de Desarrollo Urbano y Transporte - DGROC CATASTRO</t>
         </is>
       </c>
       <c r="B852" s="5" t="n">
@@ -11533,7 +11533,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>TU01CUX05  Necesito ayuda - Seguridad turística</t>
+          <t>TR03CUX25 Cómo pagar boletas - Ministerio de Desarrollo Urbano y Transporte - DGROC CATASTRO</t>
         </is>
       </c>
       <c r="B853" s="5" t="n">
@@ -11546,7 +11546,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>TU01CUX05 Perdí mi pasaporte - Seguridad turística</t>
+          <t>TR03CUX27 Denuncia de venta de dominio - Ministerio de Justicia y Seguridad</t>
         </is>
       </c>
       <c r="B854" s="5" t="n">
@@ -11559,7 +11559,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>SA08CUX02 Quiero ser donante - Donación de órganos ??</t>
+          <t>TR03CUX27 Retiro del vehículo acarreado abandonado - Ministerio de Justicia y Seguridad</t>
         </is>
       </c>
       <c r="B855" s="5" t="n">
@@ -11572,7 +11572,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>MO10CUX03 Líneas - Metrobus del Norte</t>
+          <t>DH11CUX07 Video 1 - Geolocalizacion virtual</t>
         </is>
       </c>
       <c r="B856" s="5" t="n">
@@ -11585,7 +11585,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>MO10CUX04 Apertura - Metrobus Juan B. Justo</t>
+          <t>DH11CUX05 V3 - Curso Fotoproducto virtual</t>
         </is>
       </c>
       <c r="B857" s="5" t="n">
@@ -11598,7 +11598,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>MO10CUX04 Combinaciones - Metrobus Juan B. Justo</t>
+          <t>DH11CUX08 Silencio user video 1 - Compras con impacto</t>
         </is>
       </c>
       <c r="B858" s="5" t="n">
@@ -11611,7 +11611,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>MO10CUX04 Puntos de interés - Metrobus Juan B. Justo</t>
+          <t>NI01CUX02  Nunca jugué - Pin8 🤖</t>
         </is>
       </c>
       <c r="B859" s="5" t="n">
@@ -11624,7 +11624,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>MO10CUX08 Apertura - Metrobus Alberdi-Directorio</t>
+          <t>NI01CUX03  Apertura - Super chanchitos 🐷🐷🐷</t>
         </is>
       </c>
       <c r="B860" s="5" t="n">
@@ -11637,7 +11637,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>NI01CUX02  Qué empiecen a jugar - Pin8 ??</t>
+          <t>NI01CUX05 Botimisiones - Boticuentos 2023: Superapertura y CC</t>
         </is>
       </c>
       <c r="B861" s="5" t="n">
@@ -11650,7 +11650,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>13. SUA01CUX13 - Falta de conservación de fachada</t>
+          <t>NI01CUX06 A pie - Boticuentos 2023: Misión Obelisco</t>
         </is>
       </c>
       <c r="B862" s="5" t="n">
@@ -11663,7 +11663,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>SA08CUX01 Campañas de donación - Donación de sangre ??</t>
+          <t>NI01CUX06 Volando - Boticuentos 2023: Misión Obelisco</t>
         </is>
       </c>
       <c r="B863" s="5" t="n">
@@ -11676,7 +11676,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>EDU03CUX06 Cómo funciona - Escuela de Maestros</t>
+          <t>NI01CUX07 Principio - Boticuentos 2023: Misión al pasado</t>
         </is>
       </c>
       <c r="B864" s="5" t="n">
@@ -11689,7 +11689,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>CU08CUX06 Feria francesa - Verano en la Ciudad 2026</t>
+          <t>NI01CUX08 Principio - Boticuentos 2023: Misión cósmica</t>
         </is>
       </c>
       <c r="B865" s="5" t="n">
@@ -11702,7 +11702,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>CU09CUX03 Curiosidatos - Palacio Barolo</t>
+          <t>TR03CUX07 Apertura Inscripción al registro público de salvavidas - Subsecretaría de Deportes</t>
         </is>
       </c>
       <c r="B866" s="5" t="n">
@@ -11715,7 +11715,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>06. CU09CUX96 - Centro de Convenciones</t>
+          <t>TR03CUX08 Registro Nacional de Productos Alimenticios (RNPA) / Registro Nacional de Establecimientos (RNE) - AGC</t>
         </is>
       </c>
       <c r="B867" s="5" t="n">
@@ -11728,7 +11728,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>EM04CUX02 Tipos de crédito mujeres emprendedoras - Mujer Emprendedora</t>
+          <t>TUR01CUX03 Elegir tipo de turrno - Identidad de Género</t>
         </is>
       </c>
       <c r="B868" s="5" t="n">
@@ -11741,7 +11741,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>AM03CUX05 Qué puedo hacer - Superapertura Sustentabilidad</t>
+          <t>TUR01CUX03 Por fecha &gt; Sede - Identidad de Género</t>
         </is>
       </c>
       <c r="B869" s="5" t="n">
@@ -11754,7 +11754,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>AM04CUX02 Días y horarios - Jardín Botánico</t>
+          <t>GE03CUX02 Soy emprendedora - Autonomía económica</t>
         </is>
       </c>
       <c r="B870" s="5" t="n">
@@ -11767,7 +11767,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>AM04CUX03 Quiero ir - Lago Lugano</t>
+          <t>03. Iglesias y templos de la Ciudad</t>
         </is>
       </c>
       <c r="B871" s="5" t="n">
@@ -11780,7 +11780,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>AM04CUX06 Quiero ir - Reserva Ecológica Ciudad Universitaria Costanera Norte</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="B872" s="5" t="n">
@@ -11793,7 +11793,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>CU11CUX03 Parque Avellaneda (Chacra de los Remedios) - Circuito de Espacios Culturales</t>
+          <t>TU01CUX05 Perdí mi pasaporte - Seguridad turística</t>
         </is>
       </c>
       <c r="B873" s="5" t="n">
@@ -11806,7 +11806,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>DH02CUX01 Créditos emprendedores - RUPEPYS</t>
         </is>
       </c>
       <c r="B874" s="5" t="n">
@@ -11819,7 +11819,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>03. Iglesias y templos de la Ciudad</t>
+          <t>DH02CUX01 Capacitaciones - RUPEPYS</t>
         </is>
       </c>
       <c r="B875" s="5" t="n">
@@ -11832,7 +11832,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Test STT pia</t>
+          <t>GE02CUX02 Realidad histórica - Historia del 8M</t>
         </is>
       </c>
       <c r="B876" s="5" t="n">
@@ -11845,7 +11845,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>NI01CUX06 Con muchas aceitunas - Boticuentos 2023: Misión Obelisco</t>
+          <t>GE03CUX02 Integración laboral - Autonomía económica</t>
         </is>
       </c>
       <c r="B877" s="5" t="n">
@@ -11858,7 +11858,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>NI01CUX06 Principio - Boticuentos 2023: Misión Obelisco</t>
+          <t>DH02CUX01 Quiero anotarme - RUPEPYS</t>
         </is>
       </c>
       <c r="B878" s="5" t="n">
@@ -11871,7 +11871,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>NI01CUX07 Escarapela - Boticuentos 2023: Misión al pasado</t>
+          <t>CU10CUX02 Diógenes y el Linyera &gt; Contame más - Paseo de la historieta</t>
         </is>
       </c>
       <c r="B879" s="5" t="n">
@@ -11884,7 +11884,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>NI01CUX08 En bici - Boticuentos 2023: Misión cósmica</t>
+          <t>CU11CUX03 Apertura corta - Circuito de Espacios Culturales</t>
         </is>
       </c>
       <c r="B880" s="5" t="n">
@@ -11897,7 +11897,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>NI01CUX09 Sí, dale (Primer acto) - El fantasma del Anfiteatro</t>
+          <t>CU11CUX03 Chacarita (Carlos Gardel) - Circuito de Espacios Culturales</t>
         </is>
       </c>
       <c r="B881" s="5" t="n">
@@ -11910,7 +11910,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>NI01CUX10 Puesto de figuritas - El tranvía loco de Caballito</t>
+          <t>TUR01CUX03 Seleccionar hora - Por Lugar - Identidad de Género</t>
         </is>
       </c>
       <c r="B882" s="5" t="n">
@@ -11923,7 +11923,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Por lugar &gt; No sirve &gt; dirección verificada - Identidad de Género</t>
+          <t>CU08CUX06 Feria francesa - Verano en la Ciudad 2026</t>
         </is>
       </c>
       <c r="B883" s="5" t="n">
@@ -11936,7 +11936,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>Cambiar datos DNI</t>
+          <t>JU03CUX01 Qué necesito - Patrocinio penal</t>
         </is>
       </c>
       <c r="B884" s="5" t="n">
@@ -11949,7 +11949,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>VI01CUX05 Cómo me inscribo - Programa Ley 624</t>
+          <t>AM03CUX05 Apertura Corta - Superapertura Sustentabilidad</t>
         </is>
       </c>
       <c r="B885" s="5" t="n">
@@ -11962,7 +11962,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>VI01CUX05 Entrega de viviendas - Programa Ley 624</t>
+          <t>DE05CUX04 Sobre el autódromo - Autódromo</t>
         </is>
       </c>
       <c r="B886" s="5" t="n">
@@ -11975,7 +11975,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>VI01CUX06 Monto del préstamo - Refacción + Fácil</t>
+          <t>AM03CUX05 Qué puedo hacer - Superapertura Sustentabilidad</t>
         </is>
       </c>
       <c r="B887" s="5" t="n">
@@ -11988,7 +11988,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>VI01CUX06 Qué necesito - Refacción + Fácil</t>
+          <t>JU03CUX01 Conocer mis derechos - Patrocinio penal</t>
         </is>
       </c>
       <c r="B888" s="5" t="n">
@@ -11999,15 +11999,132 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" s="7" t="inlineStr">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>JU03CUX01 Cómo funciona - Patrocinio penal</t>
+        </is>
+      </c>
+      <c r="B889" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C889" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>06. CU09CUX96 - Centro de Convenciones</t>
+        </is>
+      </c>
+      <c r="B890" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C890" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>AM04CUX02 Días y horarios - Jardín Botánico</t>
+        </is>
+      </c>
+      <c r="B891" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C891" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>INN09CUX01 Cómo se genera - Firma digital</t>
+        </is>
+      </c>
+      <c r="B892" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C892" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Derivación a agente de 147</t>
+        </is>
+      </c>
+      <c r="B893" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C893" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>AM04CUX03 Quiero ir - Lago Lugano</t>
+        </is>
+      </c>
+      <c r="B894" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C894" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>a [NOMBRE AMIGABLE FALTANTE]</t>
+        </is>
+      </c>
+      <c r="B895" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C895" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>fulfilled of Insulto [NOMBRE AMIGABLE FALTANTE]</t>
+        </is>
+      </c>
+      <c r="B896" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C896" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>DDHH03CUX09 Cómo es el taller - Programa Abrazar</t>
+        </is>
+      </c>
+      <c r="B897" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C897" s="6" t="n">
+        <v>4.056778674325865e-07</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B889" s="8" t="n">
+      <c r="B898" s="8" t="n">
         <v>2465010</v>
       </c>
-      <c r="C889" s="9" t="n">
+      <c r="C898" s="9" t="n">
         <v>1</v>
       </c>
     </row>
